--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -643,7 +643,7 @@
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I5" s="6" t="inlineStr"/>
       <c r="J5" s="7" t="inlineStr"/>

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -604,7 +604,7 @@
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -604,7 +604,7 @@
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -652,6 +652,33 @@
           <t>숫자 입력</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>하나머티리얼즈</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>166090</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>1329</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -646,7 +646,9 @@
         <v>15</v>
       </c>
       <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="n">
+        <v>46218</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>숫자 입력</t>
@@ -677,8 +679,39 @@
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="7" t="inlineStr"/>
+      <c r="J6" s="7" t="n">
+        <v>46218</v>
+      </c>
       <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>테크</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>089030</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>985</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1729</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>2310</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="7" t="n">
+        <v>46218</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -706,7 +706,9 @@
       </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="n">
+        <v>30</v>
+      </c>
       <c r="I7" s="6" t="inlineStr"/>
       <c r="J7" s="7" t="n">
         <v>46218</v>

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -714,6 +714,33 @@
         <v>46218</v>
       </c>
       <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>와이씨</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>232140</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>544</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>727</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>847</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -739,8 +739,39 @@
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="7" t="inlineStr"/>
+      <c r="J8" s="7" t="n">
+        <v>46219</v>
+      </c>
       <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>319660</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1797</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>2248</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>2623</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="7" t="n">
+        <v>46219</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -772,6 +772,60 @@
         <v>46219</v>
       </c>
       <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>해성디에스</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>195870</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>936</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>1632</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="7" t="n">
+        <v>46219</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>엠케이전자</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>033160</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1096</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1714</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -824,7 +824,9 @@
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="6" t="inlineStr"/>
-      <c r="J11" s="7" t="inlineStr"/>
+      <c r="J11" s="7" t="n">
+        <v>46219</v>
+      </c>
       <c r="K11" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -828,6 +828,33 @@
         <v>46219</v>
       </c>
       <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>비에이치</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>090460</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1148</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>1429</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>1607</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -855,6 +855,31 @@
       <c r="I12" s="6" t="inlineStr"/>
       <c r="J12" s="7" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>디케이티</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>290550</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>313</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>568</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -880,6 +880,33 @@
       <c r="I13" s="6" t="inlineStr"/>
       <c r="J13" s="7" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>554</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>799</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1278</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -907,6 +907,33 @@
       <c r="I14" s="6" t="inlineStr"/>
       <c r="J14" s="7" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>대덕전자</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>353200</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>2514</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>3571</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>4453</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -934,6 +934,33 @@
       <c r="I15" s="6" t="inlineStr"/>
       <c r="J15" s="7" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>유진테크</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>084370</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1027</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>1319</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>1390</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="6" t="inlineStr"/>
+      <c r="J16" s="7" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -961,6 +961,33 @@
       <c r="I16" s="6" t="inlineStr"/>
       <c r="J16" s="7" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>036930</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>602</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>1535</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>3165</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -988,6 +988,33 @@
       <c r="I17" s="6" t="inlineStr"/>
       <c r="J17" s="7" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>095610</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1014</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>1348</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>1823</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="7" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1015,6 +1015,33 @@
       <c r="I18" s="6" t="inlineStr"/>
       <c r="J18" s="7" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>240810</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1872</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>2717</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>3401</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1042,6 +1042,60 @@
       <c r="I19" s="6" t="inlineStr"/>
       <c r="J19" s="7" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>이엔에프테크놀로지</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>102710</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>823</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>1181</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>1670</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>한솔케미칼</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>014680</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1889</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>2374</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>2983</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1096,6 +1096,27 @@
       <c r="I21" s="6" t="inlineStr"/>
       <c r="J21" s="7" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>동진쎄미켐</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>005290</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1117,6 +1117,33 @@
       <c r="I22" s="6" t="inlineStr"/>
       <c r="J22" s="7" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>원익머트리얼즈</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>104830</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>719</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>922</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1144,6 +1144,33 @@
       <c r="I23" s="6" t="inlineStr"/>
       <c r="J23" s="7" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SKC</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>011790</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>-605</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>845</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>2399</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr"/>
+      <c r="J24" s="7" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1171,6 +1171,33 @@
       <c r="I24" s="6" t="inlineStr"/>
       <c r="J24" s="7" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>원익QnC</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>074600</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1081</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>1407</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>1638</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1198,6 +1198,33 @@
       <c r="I25" s="6" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>252990</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>319</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>427</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>486</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1225,6 +1225,33 @@
       <c r="I26" s="6" t="inlineStr"/>
       <c r="J26" s="7" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>비씨엔씨</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>146320</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1252,6 +1252,27 @@
       <c r="I27" s="6" t="inlineStr"/>
       <c r="J27" s="7" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>에스앤에스텍</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>101490</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr"/>
+      <c r="J28" s="7" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1273,6 +1273,54 @@
       <c r="I28" s="6" t="inlineStr"/>
       <c r="J28" s="7" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>솔브레인</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>357780</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>1941</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>2518</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>3133</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>디엔에프</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>092070</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="6" t="inlineStr"/>
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1321,6 +1321,60 @@
       <c r="I30" s="6" t="inlineStr"/>
       <c r="J30" s="7" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>하나마이크론</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>067310</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>3155</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>3786</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SFA반도체</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>036540</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>703</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>897</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="6" t="inlineStr"/>
+      <c r="J32" s="7" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1347,7 +1347,11 @@
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="6" t="inlineStr"/>
       <c r="J31" s="7" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>OSAT</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1374,7 +1378,38 @@
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="6" t="inlineStr"/>
       <c r="J32" s="7" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>OSAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>두산테스나</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>131970</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>484</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>1131</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>1335</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="7" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1410,6 +1410,33 @@
       <c r="I33" s="6" t="inlineStr"/>
       <c r="J33" s="7" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>네패스</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>033640</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>411</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>522</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="6" t="inlineStr"/>
+      <c r="J34" s="7" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1437,6 +1437,33 @@
       <c r="I34" s="6" t="inlineStr"/>
       <c r="J34" s="7" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>네패스아크</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>330860</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>269</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>442</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>589</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="7" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1464,6 +1464,27 @@
       <c r="I35" s="6" t="inlineStr"/>
       <c r="J35" s="7" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LB세미콘</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>061970</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="6" t="inlineStr"/>
+      <c r="J36" s="7" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1485,6 +1485,27 @@
       <c r="I36" s="6" t="inlineStr"/>
       <c r="J36" s="7" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>한양디지텍</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>078350</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="5" t="inlineStr"/>
+      <c r="I37" s="6" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1506,6 +1506,29 @@
       <c r="I37" s="6" t="inlineStr"/>
       <c r="J37" s="7" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>디아이티</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>110990</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>485</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="7" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1529,6 +1529,33 @@
       <c r="I38" s="6" t="inlineStr"/>
       <c r="J38" s="7" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>089970</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>965</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>1357</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>1554</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1387,22 +1387,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>033640</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>484</v>
+        <v>411</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1131</v>
+        <v>522</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1335</v>
+        <v>620</v>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr"/>
@@ -1414,22 +1414,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>네패스아크</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>033640</t>
+          <t>330860</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>411</v>
+        <v>269</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>522</v>
+        <v>442</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>620</v>
+        <v>589</v>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr"/>
@@ -1441,23 +1441,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>네패스아크</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>330860</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>269</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>442</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>589</v>
-      </c>
+          <t>061970</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
@@ -1468,12 +1462,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>061970</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -1489,15 +1483,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>디아이티</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>078350</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr"/>
+          <t>110990</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>485</v>
+      </c>
       <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr"/>
@@ -1510,19 +1506,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>디아이티</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>110990</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>485</v>
-      </c>
-      <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
+        <v>965</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>1357</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>1554</v>
+      </c>
       <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
@@ -1533,22 +1533,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>경동나비엔</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>009450</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>965</v>
+        <v>2377</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>1357</v>
+        <v>2693</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1554</v>
+        <v>3174</v>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr"/>
@@ -1556,6 +1556,87 @@
       <c r="I39" s="6" t="inlineStr"/>
       <c r="J39" s="7" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>003490</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>8775</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>20815</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>24999</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="7" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>두산테스나</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>131970</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>484</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>1131</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>1335</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>디아이</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>003160</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>967</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>1151</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>1241</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="6" t="inlineStr"/>
+      <c r="J42" s="7" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -1483,19 +1483,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>디아이티</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>110990</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>485</v>
-      </c>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr"/>
+        <v>965</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>1357</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>1554</v>
+      </c>
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
@@ -1506,22 +1510,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>경동나비엔</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>009450</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>965</v>
+        <v>2377</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>1357</v>
+        <v>2693</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1554</v>
+        <v>3174</v>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="inlineStr"/>
@@ -1533,22 +1537,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>경동나비엔</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>009450</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2377</v>
+        <v>8775</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>2693</v>
+        <v>20815</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>3174</v>
+        <v>24999</v>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr"/>
@@ -1560,22 +1564,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>8775</v>
+        <v>484</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>20815</v>
+        <v>1131</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>24999</v>
+        <v>1335</v>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="inlineStr"/>
@@ -1587,22 +1591,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>디아이</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>003160</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>484</v>
+        <v>967</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>1131</v>
+        <v>1151</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1335</v>
+        <v>1241</v>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr"/>
@@ -1614,23 +1618,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>디아이</t>
+          <t>디아이티</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>003160</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>967</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>1151</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>1241</v>
-      </c>
+          <t>110990</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr"/>
       <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -584,100 +584,92 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>650</v>
+        <v>1289</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1076</v>
+        <v>1707</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1357</v>
+        <v>2083</v>
       </c>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>사용자 추정</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
       <c r="J4" s="7" t="n">
         <v>46218</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>예시값</t>
+          <t>숫자 입력</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>166090</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1289</v>
+        <v>1002</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1707</v>
+        <v>1329</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2083</v>
+        <v>1450</v>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="5" t="n">
-        <v>15</v>
-      </c>
+      <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="6" t="inlineStr"/>
       <c r="J5" s="7" t="n">
         <v>46218</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>숫자 입력</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>테크</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>089030</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1002</v>
+        <v>985</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1329</v>
+        <v>1729</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1450</v>
+        <v>2310</v>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="n">
+        <v>30</v>
+      </c>
       <c r="I6" s="6" t="inlineStr"/>
       <c r="J6" s="7" t="n">
         <v>46218</v>
@@ -687,53 +679,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>테크</t>
+          <t>와이씨</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>089030</t>
+          <t>232140</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>985</v>
+        <v>544</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1729</v>
+        <v>727</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2310</v>
+        <v>847</v>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="5" t="n">
-        <v>30</v>
-      </c>
+      <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr"/>
       <c r="J7" s="7" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>와이씨</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>232140</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>544</v>
+        <v>1797</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>727</v>
+        <v>2248</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>847</v>
+        <v>2623</v>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr"/>
@@ -747,22 +737,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>해성디에스</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>195870</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1797</v>
+        <v>936</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2248</v>
+        <v>1340</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2623</v>
+        <v>1632</v>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr"/>
@@ -776,23 +766,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>해성디에스</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>195870</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>936</v>
+        <v>1096</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1340</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>1632</v>
-      </c>
+        <v>1714</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
@@ -805,50 +793,48 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>비에이치</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>090460</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1096</v>
+        <v>1148</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1714</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
+        <v>1429</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>1607</v>
+      </c>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="6" t="inlineStr"/>
-      <c r="J11" s="7" t="n">
-        <v>46219</v>
-      </c>
+      <c r="J11" s="7" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>비에이치</t>
+          <t>디케이티</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>090460</t>
+          <t>290550</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1148</v>
+        <v>313</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1429</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>1607</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
@@ -859,21 +845,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>디케이티</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>290550</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>313</v>
+        <v>554</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>568</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
+        <v>799</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>1278</v>
+      </c>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr"/>
@@ -884,22 +872,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>353200</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>554</v>
+        <v>2514</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>799</v>
+        <v>3571</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1278</v>
+        <v>4453</v>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr"/>
@@ -911,22 +899,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>유진테크</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>084370</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2514</v>
+        <v>1027</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3571</v>
+        <v>1319</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4453</v>
+        <v>1390</v>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr"/>
@@ -938,22 +926,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>유진테크</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>084370</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1027</v>
+        <v>602</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1319</v>
+        <v>1535</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1390</v>
+        <v>3165</v>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr"/>
@@ -965,22 +953,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>602</v>
+        <v>1014</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1535</v>
+        <v>1348</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3165</v>
+        <v>1823</v>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
@@ -992,22 +980,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1014</v>
+        <v>1872</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1348</v>
+        <v>2717</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1823</v>
+        <v>3401</v>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr"/>
@@ -1019,22 +1007,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>102710</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1872</v>
+        <v>823</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2717</v>
+        <v>1181</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3401</v>
+        <v>1670</v>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr"/>
@@ -1046,22 +1034,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>102710</t>
+          <t>014680</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>823</v>
+        <v>1889</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1181</v>
+        <v>2374</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1670</v>
+        <v>2983</v>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr"/>
@@ -1073,23 +1061,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>014680</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1889</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>2374</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>2983</v>
-      </c>
+          <t>005290</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
@@ -1100,17 +1082,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>005290</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
+          <t>104830</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>719</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>922</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>1040</v>
+      </c>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
@@ -1121,22 +1109,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>SKC</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>104830</t>
+          <t>011790</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>719</v>
+        <v>-605</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>922</v>
+        <v>845</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1040</v>
+        <v>2399</v>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr"/>
@@ -1148,22 +1136,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SKC</t>
+          <t>원익QnC</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>011790</t>
+          <t>074600</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-605</v>
+        <v>1081</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>845</v>
+        <v>1407</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2399</v>
+        <v>1638</v>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr"/>
@@ -1175,22 +1163,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>원익QnC</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>074600</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1081</v>
+        <v>319</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1407</v>
+        <v>427</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1638</v>
+        <v>486</v>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr"/>
@@ -1202,22 +1190,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>비씨엔씨</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>146320</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>319</v>
+        <v>93</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>427</v>
+        <v>162</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>486</v>
+        <v>219</v>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr"/>
@@ -1229,23 +1217,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>비씨엔씨</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>146320</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>162</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>219</v>
-      </c>
+          <t>101490</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
@@ -1256,17 +1238,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>에스앤에스텍</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>101490</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr"/>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr"/>
+          <t>357780</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>1941</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>2518</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>3133</v>
+      </c>
       <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
@@ -1277,23 +1265,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>디엔에프</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>357780</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>1941</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>2518</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>3133</v>
-      </c>
+          <t>092070</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
       <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
@@ -1304,43 +1286,53 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>디엔에프</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>092070</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr"/>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr"/>
+          <t>067310</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>3155</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>3786</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>4361</v>
+      </c>
       <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="6" t="inlineStr"/>
       <c r="J30" s="7" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>OSAT</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3155</v>
+        <v>60</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3786</v>
+        <v>703</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4361</v>
+        <v>897</v>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr"/>
@@ -1356,53 +1348,49 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>033640</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>60</v>
+        <v>411</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>703</v>
+        <v>522</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>897</v>
+        <v>620</v>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="6" t="inlineStr"/>
       <c r="J32" s="7" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>OSAT</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>네패스아크</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>033640</t>
+          <t>330860</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>411</v>
+        <v>269</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>522</v>
+        <v>442</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>620</v>
+        <v>589</v>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr"/>
@@ -1414,23 +1402,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>네패스아크</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>330860</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>269</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>442</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>589</v>
-      </c>
+          <t>061970</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr"/>
       <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
@@ -1441,12 +1423,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>061970</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -1462,17 +1444,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>078350</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr"/>
-      <c r="D36" s="4" t="inlineStr"/>
-      <c r="E36" s="4" t="inlineStr"/>
+          <t>089970</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>965</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>1357</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>1554</v>
+      </c>
       <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
@@ -1483,22 +1471,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>경동나비엔</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>009450</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>965</v>
+        <v>2377</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>1357</v>
+        <v>2693</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1554</v>
+        <v>3174</v>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr"/>
@@ -1510,22 +1498,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>경동나비엔</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>009450</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>2377</v>
+        <v>8775</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>2693</v>
+        <v>20815</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>3174</v>
+        <v>24999</v>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="inlineStr"/>
@@ -1537,22 +1525,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>8775</v>
+        <v>484</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>20815</v>
+        <v>1131</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>24999</v>
+        <v>1335</v>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr"/>
@@ -1564,22 +1552,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>디아이</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>003160</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>484</v>
+        <v>967</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>1131</v>
+        <v>1151</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1335</v>
+        <v>1241</v>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="inlineStr"/>
@@ -1591,23 +1579,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>디아이</t>
+          <t>디아이티</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>003160</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>967</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>1151</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>1241</v>
-      </c>
+          <t>110990</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
@@ -1618,23 +1600,239 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>디아이티</t>
+          <t>롯데관광개발</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>110990</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr"/>
-      <c r="D42" s="4" t="inlineStr"/>
-      <c r="E42" s="4" t="inlineStr"/>
+          <t>032350</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>2425</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>2685</v>
+      </c>
       <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="6" t="inlineStr"/>
       <c r="J42" s="7" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>산일전기</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>062040</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>2517</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>3337</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>4247</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="7" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>세진중공업</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>075580</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>861</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>1010</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>1056</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr"/>
+      <c r="J44" s="7" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>3532</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>4124</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="5" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="7" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>싸이맥스</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>160980</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="7" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>에스티아이</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>039440</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>751</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>1306</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>1341</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="6" t="inlineStr"/>
+      <c r="J47" s="7" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>231</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>371</v>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr"/>
+      <c r="I48" s="6" t="inlineStr"/>
+      <c r="J48" s="7" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>엑시콘</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>092870</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>282</v>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="5" t="inlineStr"/>
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>650</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>1076</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>1357</v>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="5" t="inlineStr"/>
+      <c r="I50" s="6" t="inlineStr"/>
+      <c r="J50" s="7" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -679,22 +679,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>와이씨</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>232140</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>544</v>
+        <v>1797</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>727</v>
+        <v>2248</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>847</v>
+        <v>2623</v>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr"/>
@@ -708,22 +708,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>해성디에스</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>195870</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1797</v>
+        <v>936</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2248</v>
+        <v>1340</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2623</v>
+        <v>1632</v>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr"/>
@@ -737,78 +737,74 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>해성디에스</t>
+          <t>비에이치</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>195870</t>
+          <t>090460</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>936</v>
+        <v>1148</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1340</v>
+        <v>1429</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1632</v>
+        <v>1607</v>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="7" t="n">
-        <v>46219</v>
-      </c>
+      <c r="J9" s="7" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>디케이티</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>290550</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1096</v>
+        <v>313</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1714</v>
+        <v>568</v>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="7" t="n">
-        <v>46219</v>
-      </c>
+      <c r="J10" s="7" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>비에이치</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>090460</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1148</v>
+        <v>554</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1429</v>
+        <v>799</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1607</v>
+        <v>1278</v>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
@@ -820,21 +816,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>디케이티</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>290550</t>
+          <t>353200</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>313</v>
+        <v>2514</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>568</v>
-      </c>
-      <c r="E12" s="4" t="inlineStr"/>
+        <v>3571</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>4453</v>
+      </c>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
@@ -845,22 +843,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>유진테크</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>084370</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>554</v>
+        <v>1027</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>799</v>
+        <v>1319</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1278</v>
+        <v>1390</v>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr"/>
@@ -872,22 +870,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2514</v>
+        <v>602</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3571</v>
+        <v>1535</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4453</v>
+        <v>3165</v>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr"/>
@@ -899,22 +897,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>유진테크</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>084370</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1027</v>
+        <v>1014</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1319</v>
+        <v>1348</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1390</v>
+        <v>1823</v>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr"/>
@@ -926,22 +924,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>602</v>
+        <v>1872</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1535</v>
+        <v>2717</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3165</v>
+        <v>3401</v>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr"/>
@@ -953,22 +951,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>102710</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1014</v>
+        <v>823</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1348</v>
+        <v>1181</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1823</v>
+        <v>1670</v>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
@@ -980,22 +978,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>014680</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1872</v>
+        <v>1889</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2717</v>
+        <v>2374</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3401</v>
+        <v>2983</v>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr"/>
@@ -1007,23 +1005,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>102710</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>823</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>1181</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>1670</v>
-      </c>
+          <t>005290</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr"/>
@@ -1034,22 +1026,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>014680</t>
+          <t>104830</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1889</v>
+        <v>719</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2374</v>
+        <v>922</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2983</v>
+        <v>1040</v>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr"/>
@@ -1061,17 +1053,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>SKC</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>005290</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
+          <t>011790</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>-605</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>845</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>2399</v>
+      </c>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
@@ -1082,22 +1080,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>원익QnC</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>104830</t>
+          <t>074600</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>719</v>
+        <v>1081</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>922</v>
+        <v>1407</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1040</v>
+        <v>1638</v>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr"/>
@@ -1109,22 +1107,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SKC</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>011790</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-605</v>
+        <v>319</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>845</v>
+        <v>427</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2399</v>
+        <v>486</v>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr"/>
@@ -1136,22 +1134,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>원익QnC</t>
+          <t>비씨엔씨</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>074600</t>
+          <t>146320</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1081</v>
+        <v>93</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1407</v>
+        <v>162</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1638</v>
+        <v>219</v>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr"/>
@@ -1163,23 +1161,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>252990</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>319</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>427</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>486</v>
-      </c>
+          <t>101490</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
@@ -1190,22 +1182,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>비씨엔씨</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>146320</t>
+          <t>357780</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>93</v>
+        <v>1941</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>162</v>
+        <v>2518</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>219</v>
+        <v>3133</v>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr"/>
@@ -1217,12 +1209,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>에스앤에스텍</t>
+          <t>디엔에프</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>101490</t>
+          <t>092070</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -1238,133 +1230,133 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>357780</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1941</v>
+        <v>3155</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2518</v>
+        <v>3786</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3133</v>
+        <v>4361</v>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="6" t="inlineStr"/>
       <c r="J28" s="7" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>OSAT</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>디엔에프</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>092070</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr"/>
+          <t>036540</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>703</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>897</v>
+      </c>
       <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="6" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>OSAT</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>033640</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3155</v>
+        <v>411</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3786</v>
+        <v>522</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4361</v>
+        <v>620</v>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="6" t="inlineStr"/>
       <c r="J30" s="7" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>OSAT</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>네패스아크</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>330860</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>60</v>
+        <v>269</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>703</v>
+        <v>442</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>897</v>
+        <v>589</v>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="6" t="inlineStr"/>
       <c r="J31" s="7" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>OSAT</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>033640</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>411</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>522</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>620</v>
-      </c>
+          <t>061970</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr"/>
       <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
@@ -1375,23 +1367,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>네패스아크</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>330860</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>269</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>442</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>589</v>
-      </c>
+          <t>078350</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr"/>
       <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
@@ -1402,17 +1388,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>061970</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
+          <t>089970</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>965</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>1357</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>1554</v>
+      </c>
       <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
@@ -1423,17 +1415,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>경동나비엔</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>078350</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr"/>
-      <c r="D35" s="4" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr"/>
+          <t>009450</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>2377</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>2693</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>3174</v>
+      </c>
       <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
@@ -1444,22 +1442,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>965</v>
+        <v>8775</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>1357</v>
+        <v>20815</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1554</v>
+        <v>24999</v>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="inlineStr"/>
@@ -1471,22 +1469,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>경동나비엔</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>009450</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>2377</v>
+        <v>484</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>2693</v>
+        <v>1131</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>3174</v>
+        <v>1335</v>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr"/>
@@ -1498,22 +1496,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>디아이</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>003160</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>8775</v>
+        <v>967</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>20815</v>
+        <v>1151</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>24999</v>
+        <v>1241</v>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="inlineStr"/>
@@ -1525,23 +1523,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>디아이티</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>131970</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>484</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>1131</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>1335</v>
-      </c>
+          <t>110990</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
@@ -1552,22 +1544,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>디아이</t>
+          <t>롯데관광개발</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>003160</t>
+          <t>032350</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>967</v>
+        <v>1995</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>1151</v>
+        <v>2425</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1241</v>
+        <v>2685</v>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="inlineStr"/>
@@ -1579,17 +1571,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>디아이티</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>110990</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr"/>
-      <c r="D41" s="4" t="inlineStr"/>
-      <c r="E41" s="4" t="inlineStr"/>
+          <t>062040</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>2517</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>3337</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>4247</v>
+      </c>
       <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
@@ -1600,22 +1598,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>롯데관광개발</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>032350</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1995</v>
+        <v>861</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>2425</v>
+        <v>1010</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>2685</v>
+        <v>1056</v>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="inlineStr"/>
@@ -1627,22 +1625,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>2517</v>
+        <v>2750</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>3337</v>
+        <v>3532</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>4247</v>
+        <v>4124</v>
       </c>
       <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="inlineStr"/>
@@ -1654,23 +1652,21 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>싸이맥스</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>160980</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>861</v>
+        <v>260</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>1010</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>1056</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
@@ -1681,22 +1677,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>039440</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>2750</v>
+        <v>751</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>3532</v>
+        <v>1306</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>4124</v>
+        <v>1341</v>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="inlineStr"/>
@@ -1708,19 +1704,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>싸이맥스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>160980</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>260</v>
+        <v>231</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>450</v>
+        <v>371</v>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr"/>
@@ -1733,23 +1729,21 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>엑시콘</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>039440</t>
+          <t>092870</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>751</v>
+        <v>148</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>1306</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>1341</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr"/>
       <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
@@ -1760,21 +1754,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>231</v>
+        <v>650</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>371</v>
-      </c>
-      <c r="E48" s="4" t="inlineStr"/>
+        <v>1076</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>1357</v>
+      </c>
       <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
@@ -1785,19 +1781,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>엑시콘</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>092870</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>148</v>
+        <v>1096</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>282</v>
+        <v>1714</v>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
       <c r="F49" s="4" t="inlineStr"/>
@@ -1810,22 +1806,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>와이씨</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>232140</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>650</v>
+        <v>545</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>1076</v>
+        <v>726</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1357</v>
+        <v>847</v>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="inlineStr"/>

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -843,22 +843,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>유진테크</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>084370</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1027</v>
+        <v>602</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1319</v>
+        <v>1535</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1390</v>
+        <v>3165</v>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr"/>
@@ -870,22 +870,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>602</v>
+        <v>1014</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1535</v>
+        <v>1348</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3165</v>
+        <v>1823</v>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr"/>
@@ -897,22 +897,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>014680</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1014</v>
+        <v>1889</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1348</v>
+        <v>2374</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1823</v>
+        <v>2983</v>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr"/>
@@ -924,23 +924,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>240810</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>1872</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>2717</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>3401</v>
-      </c>
+          <t>005290</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
@@ -951,22 +945,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>102710</t>
+          <t>104830</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>823</v>
+        <v>719</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1181</v>
+        <v>922</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1670</v>
+        <v>1040</v>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
@@ -978,22 +972,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>SKC</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>014680</t>
+          <t>011790</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1889</v>
+        <v>-605</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2374</v>
+        <v>845</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2983</v>
+        <v>2399</v>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr"/>
@@ -1005,17 +999,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>005290</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
+          <t>252990</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>319</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>427</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>486</v>
+      </c>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr"/>
@@ -1026,22 +1026,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>비씨엔씨</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>104830</t>
+          <t>146320</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>719</v>
+        <v>93</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>922</v>
+        <v>162</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1040</v>
+        <v>219</v>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr"/>
@@ -1053,23 +1053,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SKC</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>011790</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>-605</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>845</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>2399</v>
-      </c>
+          <t>101490</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
@@ -1080,22 +1074,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>원익QnC</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>074600</t>
+          <t>357780</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1081</v>
+        <v>1941</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1407</v>
+        <v>2518</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1638</v>
+        <v>3133</v>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr"/>
@@ -1107,23 +1101,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>디엔에프</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>252990</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>319</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>427</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>486</v>
-      </c>
+          <t>092070</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
@@ -1134,70 +1122,84 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>비씨엔씨</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>146320</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>93</v>
+        <v>3155</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>162</v>
+        <v>3786</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>219</v>
+        <v>4361</v>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="6" t="inlineStr"/>
       <c r="J24" s="7" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>OSAT</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>에스앤에스텍</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>101490</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr"/>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr"/>
+          <t>036540</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>703</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>897</v>
+      </c>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="6" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>OSAT</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>357780</t>
+          <t>033640</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1941</v>
+        <v>411</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2518</v>
+        <v>522</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3133</v>
+        <v>620</v>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr"/>
@@ -1209,17 +1211,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>디엔에프</t>
+          <t>네패스아크</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>092070</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
+          <t>330860</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>269</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>442</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>589</v>
+      </c>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
@@ -1230,84 +1238,64 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>067310</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>3155</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>3786</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>4361</v>
-      </c>
+          <t>061970</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
       <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="6" t="inlineStr"/>
       <c r="J28" s="7" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>OSAT</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>036540</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>703</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>897</v>
-      </c>
+          <t>078350</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
       <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="6" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>OSAT</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>033640</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>411</v>
+        <v>965</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>522</v>
+        <v>1357</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>620</v>
+        <v>1554</v>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="inlineStr"/>
@@ -1319,22 +1307,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>네패스아크</t>
+          <t>경동나비엔</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>330860</t>
+          <t>009450</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>269</v>
+        <v>2377</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>442</v>
+        <v>2693</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>589</v>
+        <v>3174</v>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr"/>
@@ -1346,17 +1334,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>061970</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr"/>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
+          <t>003490</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>8775</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>20815</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>24999</v>
+      </c>
       <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
@@ -1367,17 +1361,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>078350</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
+          <t>131970</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>484</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>1131</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>1335</v>
+      </c>
       <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
@@ -1388,22 +1388,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>디아이</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>003160</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1357</v>
+        <v>1151</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1554</v>
+        <v>1241</v>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr"/>
@@ -1415,23 +1415,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>경동나비엔</t>
+          <t>디아이티</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>009450</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>2377</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>2693</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>3174</v>
-      </c>
+          <t>110990</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
@@ -1442,22 +1436,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>롯데관광개발</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>032350</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>8775</v>
+        <v>1995</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>20815</v>
+        <v>2425</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>24999</v>
+        <v>2685</v>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="inlineStr"/>
@@ -1469,22 +1463,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>484</v>
+        <v>2517</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>1131</v>
+        <v>3337</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1335</v>
+        <v>4247</v>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr"/>
@@ -1496,22 +1490,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>디아이</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>003160</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>967</v>
+        <v>861</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>1151</v>
+        <v>1010</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1241</v>
+        <v>1056</v>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="inlineStr"/>
@@ -1523,17 +1517,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>디아이티</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>110990</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr"/>
-      <c r="D39" s="4" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr"/>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>3532</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>4124</v>
+      </c>
       <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
@@ -1544,23 +1544,21 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>롯데관광개발</t>
+          <t>싸이맥스</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>032350</t>
+          <t>160980</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1995</v>
+        <v>260</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>2425</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>2685</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
@@ -1571,22 +1569,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>039440</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>2517</v>
+        <v>751</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>3337</v>
+        <v>1306</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>4247</v>
+        <v>1341</v>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr"/>
@@ -1598,23 +1596,21 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>861</v>
+        <v>231</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>1010</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>1056</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
       <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
@@ -1625,23 +1621,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>엑시콘</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>092870</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>2750</v>
+        <v>148</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>3532</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>4124</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
@@ -1652,21 +1646,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>싸이맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>160980</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>260</v>
+        <v>650</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="E44" s="4" t="inlineStr"/>
+        <v>1076</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>1357</v>
+      </c>
       <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
@@ -1677,23 +1673,21 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>039440</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>751</v>
+        <v>1096</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>1306</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>1341</v>
-      </c>
+        <v>1714</v>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
@@ -1704,21 +1698,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>와이씨</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>232140</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>231</v>
+        <v>545</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>371</v>
-      </c>
-      <c r="E46" s="4" t="inlineStr"/>
+        <v>726</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>847</v>
+      </c>
       <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
@@ -1729,21 +1725,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>엑시콘</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>092870</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>148</v>
+        <v>1861</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="E47" s="4" t="inlineStr"/>
+        <v>2611</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>3176</v>
+      </c>
       <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
@@ -1754,22 +1752,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>원익QNC</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>074600</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>650</v>
+        <v>1081</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>1076</v>
+        <v>1407</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1357</v>
+        <v>1638</v>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="inlineStr"/>
@@ -1781,21 +1779,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>유진테크</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>084370</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1096</v>
+        <v>1027</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>1714</v>
-      </c>
-      <c r="E49" s="4" t="inlineStr"/>
+        <v>1319</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>1390</v>
+      </c>
       <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
@@ -1806,22 +1806,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>와이씨</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>232140</t>
+          <t>102710</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>545</v>
+        <v>823</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>726</v>
+        <v>1181</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>847</v>
+        <v>1670</v>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="inlineStr"/>
@@ -1829,6 +1829,60 @@
       <c r="I50" s="6" t="inlineStr"/>
       <c r="J50" s="7" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>이오테크닉스</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>039030</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>1953</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>2540</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>3193</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr"/>
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="7" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>제이엔티씨</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>204270</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>540</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>1637</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>1920</v>
+      </c>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="6" t="inlineStr"/>
+      <c r="J52" s="7" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -584,175 +584,161 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>166090</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1289</v>
+        <v>1002</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1707</v>
+        <v>1329</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2083</v>
+        <v>1450</v>
       </c>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="5" t="n">
-        <v>15</v>
-      </c>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="6" t="inlineStr"/>
       <c r="J4" s="7" t="n">
         <v>46218</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>숫자 입력</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1002</v>
+        <v>1797</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1329</v>
+        <v>2248</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1450</v>
+        <v>2623</v>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="6" t="inlineStr"/>
       <c r="J5" s="7" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>테크</t>
+          <t>해성디에스</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>089030</t>
+          <t>195870</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>985</v>
+        <v>936</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1729</v>
+        <v>1340</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2310</v>
+        <v>1632</v>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="5" t="n">
-        <v>30</v>
-      </c>
+      <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="6" t="inlineStr"/>
       <c r="J6" s="7" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>비에이치</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>090460</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1797</v>
+        <v>1148</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2248</v>
+        <v>1429</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2623</v>
+        <v>1607</v>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="7" t="n">
-        <v>46219</v>
-      </c>
+      <c r="J7" s="7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>해성디에스</t>
+          <t>디케이티</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>195870</t>
+          <t>290550</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>936</v>
+        <v>313</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1340</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>1632</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="7" t="n">
-        <v>46219</v>
-      </c>
+      <c r="J8" s="7" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>비에이치</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>090460</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1148</v>
+        <v>554</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1429</v>
+        <v>799</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1607</v>
+        <v>1278</v>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr"/>
@@ -764,21 +750,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>디케이티</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>290550</t>
+          <t>353200</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>313</v>
+        <v>2514</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>568</v>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
+        <v>3571</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>4453</v>
+      </c>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
@@ -789,22 +777,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>554</v>
+        <v>602</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>799</v>
+        <v>1535</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1278</v>
+        <v>3165</v>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
@@ -816,22 +804,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2514</v>
+        <v>1014</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3571</v>
+        <v>1348</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4453</v>
+        <v>1823</v>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr"/>
@@ -843,22 +831,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>014680</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>602</v>
+        <v>1889</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1535</v>
+        <v>2374</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3165</v>
+        <v>2983</v>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr"/>
@@ -870,23 +858,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>095610</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>1014</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>1348</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>1823</v>
-      </c>
+          <t>005290</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
@@ -897,22 +879,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>014680</t>
+          <t>104830</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1889</v>
+        <v>719</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2374</v>
+        <v>922</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2983</v>
+        <v>1040</v>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr"/>
@@ -924,17 +906,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>SKC</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>005290</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
+          <t>011790</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>-605</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>845</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>2399</v>
+      </c>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
@@ -945,22 +933,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>104830</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>719</v>
+        <v>319</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>922</v>
+        <v>427</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1040</v>
+        <v>486</v>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
@@ -972,22 +960,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SKC</t>
+          <t>비씨엔씨</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>011790</t>
+          <t>146320</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-605</v>
+        <v>93</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>845</v>
+        <v>162</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2399</v>
+        <v>219</v>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr"/>
@@ -999,23 +987,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>252990</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>319</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>427</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>486</v>
-      </c>
+          <t>101490</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr"/>
@@ -1026,22 +1008,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>비씨엔씨</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>146320</t>
+          <t>357780</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>93</v>
+        <v>1941</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>162</v>
+        <v>2518</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>219</v>
+        <v>3133</v>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr"/>
@@ -1053,12 +1035,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>에스앤에스텍</t>
+          <t>디엔에프</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>101490</t>
+          <t>092070</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -1074,133 +1056,133 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>357780</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1941</v>
+        <v>3155</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2518</v>
+        <v>3786</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3133</v>
+        <v>4361</v>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="6" t="inlineStr"/>
       <c r="J22" s="7" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>OSAT</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>디엔에프</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>092070</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
+          <t>036540</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>703</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>897</v>
+      </c>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="6" t="inlineStr"/>
       <c r="J23" s="7" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>OSAT</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>033640</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3155</v>
+        <v>411</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3786</v>
+        <v>522</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4361</v>
+        <v>620</v>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="6" t="inlineStr"/>
       <c r="J24" s="7" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>OSAT</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>네패스아크</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>330860</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>60</v>
+        <v>269</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>703</v>
+        <v>442</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>897</v>
+        <v>589</v>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="6" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>OSAT</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>033640</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>411</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>522</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>620</v>
-      </c>
+          <t>061970</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
@@ -1211,23 +1193,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>네패스아크</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>330860</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>269</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>442</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>589</v>
-      </c>
+          <t>078350</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
@@ -1238,17 +1214,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>061970</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr"/>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr"/>
+          <t>089970</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>965</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>1357</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>1554</v>
+      </c>
       <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
@@ -1259,17 +1241,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>경동나비엔</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>078350</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr"/>
+          <t>009450</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>2377</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>2693</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>3174</v>
+      </c>
       <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
@@ -1280,22 +1268,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>965</v>
+        <v>8775</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1357</v>
+        <v>20815</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1554</v>
+        <v>24999</v>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="inlineStr"/>
@@ -1307,22 +1295,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>경동나비엔</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>009450</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2377</v>
+        <v>484</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2693</v>
+        <v>1131</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3174</v>
+        <v>1335</v>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr"/>
@@ -1334,22 +1322,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>디아이</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>003160</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>8775</v>
+        <v>967</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>20815</v>
+        <v>1151</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>24999</v>
+        <v>1241</v>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr"/>
@@ -1361,23 +1349,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>디아이티</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>131970</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>484</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>1131</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>1335</v>
-      </c>
+          <t>110990</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr"/>
       <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
@@ -1388,22 +1370,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>디아이</t>
+          <t>롯데관광개발</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>003160</t>
+          <t>032350</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>967</v>
+        <v>1995</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1151</v>
+        <v>2425</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1241</v>
+        <v>2685</v>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr"/>
@@ -1415,17 +1397,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>디아이티</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>110990</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr"/>
-      <c r="D35" s="4" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr"/>
+          <t>062040</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>2517</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>3337</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>4247</v>
+      </c>
       <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
@@ -1436,22 +1424,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>롯데관광개발</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>032350</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>1995</v>
+        <v>861</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>2425</v>
+        <v>1010</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>2685</v>
+        <v>1056</v>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="inlineStr"/>
@@ -1463,22 +1451,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>2517</v>
+        <v>2750</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>3337</v>
+        <v>3532</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>4247</v>
+        <v>4124</v>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr"/>
@@ -1490,23 +1478,21 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>싸이맥스</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>160980</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>861</v>
+        <v>260</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>1010</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>1056</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
@@ -1517,22 +1503,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>039440</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2750</v>
+        <v>751</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>3532</v>
+        <v>1306</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>4124</v>
+        <v>1341</v>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr"/>
@@ -1544,19 +1530,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>싸이맥스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>160980</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>260</v>
+        <v>231</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>450</v>
+        <v>371</v>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr"/>
@@ -1569,23 +1555,21 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>엑시콘</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>039440</t>
+          <t>092870</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>751</v>
+        <v>148</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>1306</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>1341</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
@@ -1596,21 +1580,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>231</v>
+        <v>650</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>371</v>
-      </c>
-      <c r="E42" s="4" t="inlineStr"/>
+        <v>1076</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>1357</v>
+      </c>
       <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
@@ -1621,19 +1607,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>엑시콘</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>092870</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>148</v>
+        <v>1096</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>282</v>
+        <v>1714</v>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr"/>
@@ -1646,22 +1632,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>와이씨</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>232140</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>650</v>
+        <v>545</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>1076</v>
+        <v>726</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1357</v>
+        <v>847</v>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="inlineStr"/>
@@ -1673,21 +1659,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1096</v>
+        <v>1861</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>1714</v>
-      </c>
-      <c r="E45" s="4" t="inlineStr"/>
+        <v>2611</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>3176</v>
+      </c>
       <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
@@ -1698,22 +1686,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>와이씨</t>
+          <t>원익QNC</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>232140</t>
+          <t>074600</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>545</v>
+        <v>1081</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>726</v>
+        <v>1407</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>847</v>
+        <v>1638</v>
       </c>
       <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="inlineStr"/>
@@ -1725,22 +1713,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>유진테크</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>084370</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1861</v>
+        <v>1027</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>2611</v>
+        <v>1319</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>3176</v>
+        <v>1390</v>
       </c>
       <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr"/>
@@ -1752,22 +1740,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>원익QNC</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>074600</t>
+          <t>102710</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1081</v>
+        <v>823</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>1407</v>
+        <v>1181</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1638</v>
+        <v>1670</v>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="inlineStr"/>
@@ -1779,22 +1767,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>유진테크</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>084370</t>
+          <t>039030</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1027</v>
+        <v>1953</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>1319</v>
+        <v>2540</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1390</v>
+        <v>3193</v>
       </c>
       <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="inlineStr"/>
@@ -1806,22 +1794,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>제이엔티씨</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>102710</t>
+          <t>204270</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>823</v>
+        <v>540</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>1181</v>
+        <v>1637</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1670</v>
+        <v>1920</v>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="inlineStr"/>
@@ -1833,22 +1821,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>039030</t>
+          <t>281820</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1953</v>
+        <v>1462</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>2540</v>
+        <v>2011</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>3193</v>
+        <v>2170</v>
       </c>
       <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="inlineStr"/>
@@ -1860,22 +1848,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>제이엔티씨</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>540</v>
+        <v>1289</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>1637</v>
+        <v>1707</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1920</v>
+        <v>2083</v>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="inlineStr"/>
@@ -1883,6 +1871,87 @@
       <c r="I52" s="6" t="inlineStr"/>
       <c r="J52" s="7" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>테크윙</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>089030</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>985</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>1729</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>2310</v>
+      </c>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr"/>
+      <c r="J53" s="7" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>064760</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>1258</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>1660</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>2109</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr"/>
+      <c r="I54" s="6" t="inlineStr"/>
+      <c r="J54" s="7" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>131290</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>1505</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>1921</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>2355</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr"/>
+      <c r="I55" s="6" t="inlineStr"/>
+      <c r="J55" s="7" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1952,6 +1952,87 @@
       <c r="I55" s="6" t="inlineStr"/>
       <c r="J55" s="7" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>440110</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>1264</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>2175</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr"/>
+      <c r="I56" s="6" t="inlineStr"/>
+      <c r="J56" s="7" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>파라다이스</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>034230</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>1881</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>2277</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>2479</v>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="5" t="inlineStr"/>
+      <c r="I57" s="6" t="inlineStr"/>
+      <c r="J57" s="7" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>2655</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>3278</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>3920</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="5" t="inlineStr"/>
+      <c r="I58" s="6" t="inlineStr"/>
+      <c r="J58" s="7" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -584,109 +584,101 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>비에이치</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>090460</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1002</v>
+        <v>1148</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1329</v>
+        <v>1429</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1450</v>
+        <v>1607</v>
       </c>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="7" t="n">
-        <v>46218</v>
-      </c>
+      <c r="J4" s="7" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>디케이티</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>290550</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1797</v>
+        <v>313</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2248</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>2623</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="7" t="n">
-        <v>46219</v>
-      </c>
+      <c r="J5" s="7" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>해성디에스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>195870</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>936</v>
+        <v>554</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1340</v>
+        <v>799</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1632</v>
+        <v>1278</v>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="7" t="n">
-        <v>46219</v>
-      </c>
+      <c r="J6" s="7" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비에이치</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>090460</t>
+          <t>353200</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1148</v>
+        <v>2514</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1429</v>
+        <v>3571</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1607</v>
+        <v>4453</v>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr"/>
@@ -698,21 +690,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>디케이티</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>290550</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>313</v>
+        <v>602</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>568</v>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
+        <v>1535</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>3165</v>
+      </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
@@ -723,22 +717,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>554</v>
+        <v>1014</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>799</v>
+        <v>1348</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1278</v>
+        <v>1823</v>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr"/>
@@ -750,22 +744,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>014680</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2514</v>
+        <v>1889</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3571</v>
+        <v>2374</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4453</v>
+        <v>2983</v>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr"/>
@@ -777,23 +771,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>036930</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>602</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>1535</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>3165</v>
-      </c>
+          <t>005290</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
@@ -804,22 +792,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>104830</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1014</v>
+        <v>719</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1348</v>
+        <v>922</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1823</v>
+        <v>1040</v>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr"/>
@@ -831,22 +819,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>SKC</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>014680</t>
+          <t>011790</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1889</v>
+        <v>-605</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2374</v>
+        <v>845</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2983</v>
+        <v>2399</v>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr"/>
@@ -858,17 +846,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>005290</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
+          <t>252990</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>319</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>427</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>486</v>
+      </c>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
@@ -879,22 +873,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>비씨엔씨</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>104830</t>
+          <t>146320</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>719</v>
+        <v>93</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>922</v>
+        <v>162</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1040</v>
+        <v>219</v>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr"/>
@@ -906,23 +900,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SKC</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>011790</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>-605</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>845</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>2399</v>
-      </c>
+          <t>101490</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
@@ -933,22 +921,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>357780</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>319</v>
+        <v>1941</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>427</v>
+        <v>2518</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>486</v>
+        <v>3133</v>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
@@ -960,23 +948,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>비씨엔씨</t>
+          <t>디엔에프</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>146320</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>162</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>219</v>
-      </c>
+          <t>092070</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
@@ -987,43 +969,53 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>에스앤에스텍</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>101490</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
+          <t>036540</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>703</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>897</v>
+      </c>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="6" t="inlineStr"/>
       <c r="J19" s="7" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>OSAT</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>357780</t>
+          <t>033640</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1941</v>
+        <v>411</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2518</v>
+        <v>522</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3133</v>
+        <v>620</v>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr"/>
@@ -1035,17 +1027,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>디엔에프</t>
+          <t>네패스아크</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>092070</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
+          <t>330860</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>269</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>442</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>589</v>
+      </c>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
@@ -1056,84 +1054,64 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>067310</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>3155</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>3786</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>4361</v>
-      </c>
+          <t>061970</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="6" t="inlineStr"/>
       <c r="J22" s="7" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>OSAT</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>036540</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>703</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>897</v>
-      </c>
+          <t>078350</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="6" t="inlineStr"/>
       <c r="J23" s="7" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>OSAT</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>033640</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>411</v>
+        <v>965</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>522</v>
+        <v>1357</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>620</v>
+        <v>1554</v>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr"/>
@@ -1145,22 +1123,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>네패스아크</t>
+          <t>경동나비엔</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>330860</t>
+          <t>009450</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>269</v>
+        <v>2377</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>442</v>
+        <v>2693</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>589</v>
+        <v>3174</v>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr"/>
@@ -1172,17 +1150,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>061970</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
+          <t>003490</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>8775</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>20815</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>24999</v>
+      </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
@@ -1193,17 +1177,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>078350</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
+          <t>131970</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>484</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>1131</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>1335</v>
+      </c>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
@@ -1214,22 +1204,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>디아이</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>003160</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1357</v>
+        <v>1151</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1554</v>
+        <v>1241</v>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="inlineStr"/>
@@ -1241,23 +1231,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>경동나비엔</t>
+          <t>디아이티</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>009450</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>2377</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>2693</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>3174</v>
-      </c>
+          <t>110990</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
       <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
@@ -1268,22 +1252,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>롯데관광개발</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>032350</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>8775</v>
+        <v>1995</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>20815</v>
+        <v>2425</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>24999</v>
+        <v>2685</v>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="inlineStr"/>
@@ -1295,22 +1279,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>484</v>
+        <v>2517</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1131</v>
+        <v>3337</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1335</v>
+        <v>4247</v>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr"/>
@@ -1322,22 +1306,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>디아이</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>003160</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>967</v>
+        <v>861</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1151</v>
+        <v>1010</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1241</v>
+        <v>1056</v>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr"/>
@@ -1349,17 +1333,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>디아이티</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>110990</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>3532</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>4124</v>
+      </c>
       <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
@@ -1370,23 +1360,21 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>롯데관광개발</t>
+          <t>싸이맥스</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>032350</t>
+          <t>160980</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1995</v>
+        <v>260</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2425</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>2685</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
       <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
@@ -1397,22 +1385,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>039440</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2517</v>
+        <v>751</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>3337</v>
+        <v>1306</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>4247</v>
+        <v>1341</v>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr"/>
@@ -1424,23 +1412,21 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>861</v>
+        <v>231</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>1010</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>1056</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
@@ -1451,23 +1437,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>엑시콘</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>092870</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>2750</v>
+        <v>148</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>3532</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>4124</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
@@ -1478,21 +1462,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>싸이맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>160980</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>260</v>
+        <v>650</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="E38" s="4" t="inlineStr"/>
+        <v>1076</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>1357</v>
+      </c>
       <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
@@ -1503,23 +1489,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>039440</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>751</v>
+        <v>1096</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>1306</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>1341</v>
-      </c>
+        <v>1714</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
@@ -1530,21 +1514,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>와이씨</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>232140</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>231</v>
+        <v>545</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>371</v>
-      </c>
-      <c r="E40" s="4" t="inlineStr"/>
+        <v>726</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>847</v>
+      </c>
       <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
@@ -1555,21 +1541,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>엑시콘</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>092870</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>148</v>
+        <v>1861</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="E41" s="4" t="inlineStr"/>
+        <v>2611</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>3176</v>
+      </c>
       <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
@@ -1580,22 +1568,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>원익QNC</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>074600</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>650</v>
+        <v>1081</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>1076</v>
+        <v>1407</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1357</v>
+        <v>1638</v>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="inlineStr"/>
@@ -1607,21 +1595,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>유진테크</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>084370</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>1096</v>
+        <v>1027</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>1714</v>
-      </c>
-      <c r="E43" s="4" t="inlineStr"/>
+        <v>1319</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>1390</v>
+      </c>
       <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
@@ -1632,22 +1622,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>와이씨</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>232140</t>
+          <t>102710</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>545</v>
+        <v>823</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>726</v>
+        <v>1181</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>847</v>
+        <v>1670</v>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="inlineStr"/>
@@ -1659,22 +1649,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>039030</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1861</v>
+        <v>1953</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>2611</v>
+        <v>2540</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>3176</v>
+        <v>3193</v>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="inlineStr"/>
@@ -1686,22 +1676,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>원익QNC</t>
+          <t>제이엔티씨</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>074600</t>
+          <t>204270</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1081</v>
+        <v>540</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>1407</v>
+        <v>1637</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1638</v>
+        <v>1920</v>
       </c>
       <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="inlineStr"/>
@@ -1713,22 +1703,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>유진테크</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>084370</t>
+          <t>281820</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1027</v>
+        <v>1462</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>1319</v>
+        <v>2011</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1390</v>
+        <v>2170</v>
       </c>
       <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr"/>
@@ -1740,22 +1730,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>102710</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>823</v>
+        <v>1289</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>1181</v>
+        <v>1707</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1670</v>
+        <v>2083</v>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="inlineStr"/>
@@ -1767,22 +1757,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>테크윙</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>039030</t>
+          <t>089030</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1953</v>
+        <v>985</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>2540</v>
+        <v>1729</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>3193</v>
+        <v>2310</v>
       </c>
       <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="inlineStr"/>
@@ -1794,22 +1784,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>제이엔티씨</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>064760</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>540</v>
+        <v>1258</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>1637</v>
+        <v>1660</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1920</v>
+        <v>2109</v>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="inlineStr"/>
@@ -1821,22 +1811,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>케이씨텍</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>281820</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1462</v>
+        <v>1505</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>2011</v>
+        <v>1921</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>2170</v>
+        <v>2355</v>
       </c>
       <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="inlineStr"/>
@@ -1848,22 +1838,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>440110</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>1289</v>
+        <v>448</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>1707</v>
+        <v>1264</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>2083</v>
+        <v>2175</v>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="inlineStr"/>
@@ -1875,22 +1865,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>테크윙</t>
+          <t>파라다이스</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>089030</t>
+          <t>034230</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>985</v>
+        <v>1881</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>1729</v>
+        <v>2277</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>2310</v>
+        <v>2479</v>
       </c>
       <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="inlineStr"/>
@@ -1902,22 +1892,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>064760</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1258</v>
+        <v>2655</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>1660</v>
+        <v>3278</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>2109</v>
+        <v>3920</v>
       </c>
       <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="inlineStr"/>
@@ -1929,22 +1919,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1505</v>
+        <v>624</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>1921</v>
+        <v>733</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>2355</v>
+        <v>750</v>
       </c>
       <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="inlineStr"/>
@@ -1956,22 +1946,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>440110</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>448</v>
+        <v>1723</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>1264</v>
+        <v>2116</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>2175</v>
+        <v>2463</v>
       </c>
       <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="inlineStr"/>
@@ -1983,22 +1973,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>파라다이스</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>034230</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1881</v>
+        <v>3154</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>2277</v>
+        <v>3785</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>2479</v>
+        <v>4361</v>
       </c>
       <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="inlineStr"/>
@@ -2010,22 +2000,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>166090</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>2655</v>
+        <v>1002</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>3278</v>
+        <v>1335</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>3920</v>
+        <v>1450</v>
       </c>
       <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="inlineStr"/>
@@ -2033,6 +2023,384 @@
       <c r="I58" s="6" t="inlineStr"/>
       <c r="J58" s="7" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>하이록코리아</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>013030</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>608</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>714</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>726</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="5" t="inlineStr"/>
+      <c r="I59" s="6" t="inlineStr"/>
+      <c r="J59" s="7" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>한국카본</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>017960</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>1798</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>1964</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>1947</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="5" t="inlineStr"/>
+      <c r="I60" s="6" t="inlineStr"/>
+      <c r="J60" s="7" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>한국항공우주</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>047810</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>4736</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>6744</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>8136</v>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+      <c r="H61" s="5" t="inlineStr"/>
+      <c r="I61" s="6" t="inlineStr"/>
+      <c r="J61" s="7" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>한화엔진</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>082740</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>2442</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>3679</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>4513</v>
+      </c>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="5" t="inlineStr"/>
+      <c r="I62" s="6" t="inlineStr"/>
+      <c r="J62" s="7" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>해성디에스</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>195870</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>897</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>1283</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>1547</v>
+      </c>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+      <c r="H63" s="5" t="inlineStr"/>
+      <c r="I63" s="6" t="inlineStr"/>
+      <c r="J63" s="7" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>001040</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>27163</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>30337</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>30852</v>
+      </c>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
+      <c r="H64" s="5" t="inlineStr"/>
+      <c r="I64" s="6" t="inlineStr"/>
+      <c r="J64" s="7" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>DB하이텍</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>000990</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>3627</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>4511</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>5191</v>
+      </c>
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
+      <c r="H65" s="5" t="inlineStr"/>
+      <c r="I65" s="6" t="inlineStr"/>
+      <c r="J65" s="7" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>HD한국조선해양</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>009540</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>55993</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>67225</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>77345</v>
+      </c>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="5" t="inlineStr"/>
+      <c r="I66" s="6" t="inlineStr"/>
+      <c r="J66" s="7" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>HD현대건설기계</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>267270</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>6821</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>8553</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>10362</v>
+      </c>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+      <c r="H67" s="5" t="inlineStr"/>
+      <c r="I67" s="6" t="inlineStr"/>
+      <c r="J67" s="7" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>HD현대마린솔루션</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>443060</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>4369</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>5517</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>6420</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
+      <c r="H68" s="5" t="inlineStr"/>
+      <c r="I68" s="6" t="inlineStr"/>
+      <c r="J68" s="7" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>HD현대마린엔진</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>071970</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>1515</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>2029</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>2509</v>
+      </c>
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr"/>
+      <c r="I69" s="6" t="inlineStr"/>
+      <c r="J69" s="7" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>403870</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>1266</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>1692</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>2054</v>
+      </c>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr"/>
+      <c r="H70" s="5" t="inlineStr"/>
+      <c r="I70" s="6" t="inlineStr"/>
+      <c r="J70" s="7" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>006260</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>16195</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>18902</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>22131</v>
+      </c>
+      <c r="F71" s="4" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr"/>
+      <c r="I71" s="6" t="inlineStr"/>
+      <c r="J71" s="7" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SNT에너지</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>100840</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>1243</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>1331</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>1407</v>
+      </c>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr"/>
+      <c r="I72" s="6" t="inlineStr"/>
+      <c r="J72" s="7" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2401,6 +2401,33 @@
       <c r="I72" s="6" t="inlineStr"/>
       <c r="J72" s="7" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>계룡건설</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>013580</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>1780</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>2130</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>2410</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr"/>
+      <c r="G73" s="4" t="inlineStr"/>
+      <c r="H73" s="5" t="inlineStr"/>
+      <c r="I73" s="6" t="inlineStr"/>
+      <c r="J73" s="7" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2428,6 +2428,33 @@
       <c r="I73" s="6" t="inlineStr"/>
       <c r="J73" s="7" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>현대이지웰</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>090850</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F74" s="4" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr"/>
+      <c r="H74" s="5" t="inlineStr"/>
+      <c r="I74" s="6" t="inlineStr"/>
+      <c r="J74" s="7" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -663,22 +663,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2514</v>
+        <v>602</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3571</v>
+        <v>1535</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4453</v>
+        <v>3165</v>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr"/>
@@ -690,22 +690,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>602</v>
+        <v>1014</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1535</v>
+        <v>1348</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3165</v>
+        <v>1823</v>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr"/>
@@ -717,22 +717,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>014680</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1014</v>
+        <v>1889</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1348</v>
+        <v>2374</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1823</v>
+        <v>2983</v>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr"/>
@@ -744,23 +744,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>014680</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1889</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>2374</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>2983</v>
-      </c>
+          <t>005290</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
@@ -771,17 +765,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>005290</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
+          <t>104830</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>719</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>922</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>1040</v>
+      </c>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
@@ -792,22 +792,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>SKC</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>104830</t>
+          <t>011790</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>719</v>
+        <v>-605</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>922</v>
+        <v>845</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1040</v>
+        <v>2399</v>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr"/>
@@ -819,22 +819,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SKC</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>011790</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-605</v>
+        <v>319</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>845</v>
+        <v>427</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2399</v>
+        <v>486</v>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr"/>
@@ -846,22 +846,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>비씨엔씨</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>146320</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>319</v>
+        <v>93</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>427</v>
+        <v>162</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>486</v>
+        <v>219</v>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr"/>
@@ -873,23 +873,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>비씨엔씨</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>146320</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>162</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>219</v>
-      </c>
+          <t>101490</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="5" t="inlineStr"/>
@@ -900,17 +894,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>에스앤에스텍</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>101490</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
+          <t>357780</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1941</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>2518</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>3133</v>
+      </c>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
@@ -921,23 +921,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>디엔에프</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>357780</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>1941</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>2518</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>3133</v>
-      </c>
+          <t>092070</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="5" t="inlineStr"/>
@@ -948,74 +942,80 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>디엔에프</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>092070</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
+          <t>036540</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>703</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>897</v>
+      </c>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="6" t="inlineStr"/>
       <c r="J18" s="7" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>OSAT</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>033640</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>60</v>
+        <v>411</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>703</v>
+        <v>522</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>897</v>
+        <v>620</v>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="6" t="inlineStr"/>
       <c r="J19" s="7" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>OSAT</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>네패스아크</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>033640</t>
+          <t>330860</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>411</v>
+        <v>269</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>522</v>
+        <v>442</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>620</v>
+        <v>589</v>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr"/>
@@ -1027,23 +1027,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>네패스아크</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>330860</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>269</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>442</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>589</v>
-      </c>
+          <t>061970</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
@@ -1054,12 +1048,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>061970</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -1075,17 +1069,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>078350</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
+          <t>089970</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>965</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>1357</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>1554</v>
+      </c>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
@@ -1096,22 +1096,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>경동나비엔</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>009450</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>965</v>
+        <v>2377</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1357</v>
+        <v>2693</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1554</v>
+        <v>3174</v>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr"/>
@@ -1123,22 +1123,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>경동나비엔</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>009450</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2377</v>
+        <v>8775</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2693</v>
+        <v>20815</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3174</v>
+        <v>24999</v>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr"/>
@@ -1150,22 +1150,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>8775</v>
+        <v>484</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>20815</v>
+        <v>1131</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>24999</v>
+        <v>1335</v>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr"/>
@@ -1177,22 +1177,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>디아이</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>003160</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>484</v>
+        <v>967</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1131</v>
+        <v>1151</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1335</v>
+        <v>1241</v>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr"/>
@@ -1204,23 +1204,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>디아이</t>
+          <t>디아이티</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>003160</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>967</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>1151</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>1241</v>
-      </c>
+          <t>110990</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
       <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
@@ -1231,17 +1225,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>디아이티</t>
+          <t>롯데관광개발</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>110990</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr"/>
+          <t>032350</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>1995</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>2425</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>2685</v>
+      </c>
       <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
@@ -1252,22 +1252,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>롯데관광개발</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>032350</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1995</v>
+        <v>2517</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2425</v>
+        <v>3337</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2685</v>
+        <v>4247</v>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="inlineStr"/>
@@ -1279,22 +1279,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2517</v>
+        <v>861</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3337</v>
+        <v>1010</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4247</v>
+        <v>1056</v>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr"/>
@@ -1306,22 +1306,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>861</v>
+        <v>2750</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1010</v>
+        <v>3532</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1056</v>
+        <v>4124</v>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr"/>
@@ -1333,23 +1333,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>싸이맥스</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>160980</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2750</v>
+        <v>260</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3532</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>4124</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
       <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
@@ -1360,21 +1358,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>싸이맥스</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>160980</t>
+          <t>039440</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>260</v>
+        <v>751</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="E34" s="4" t="inlineStr"/>
+        <v>1306</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>1341</v>
+      </c>
       <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
@@ -1385,23 +1385,21 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>039440</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>751</v>
+        <v>231</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1306</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>1341</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
@@ -1412,19 +1410,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>엑시콘</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>092870</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>231</v>
+        <v>148</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>371</v>
+        <v>282</v>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr"/>
@@ -1437,21 +1435,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>엑시콘</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>092870</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>148</v>
+        <v>650</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="E37" s="4" t="inlineStr"/>
+        <v>1076</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>1357</v>
+      </c>
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
@@ -1462,23 +1462,21 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>650</v>
+        <v>1096</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>1076</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>1357</v>
-      </c>
+        <v>1714</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
@@ -1489,21 +1487,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>와이씨</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>232140</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1096</v>
+        <v>545</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>1714</v>
-      </c>
-      <c r="E39" s="4" t="inlineStr"/>
+        <v>726</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>847</v>
+      </c>
       <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
@@ -1514,22 +1514,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>와이씨</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>232140</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>545</v>
+        <v>1861</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>726</v>
+        <v>2611</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>847</v>
+        <v>3176</v>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="inlineStr"/>
@@ -1541,22 +1541,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>원익QNC</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>074600</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1861</v>
+        <v>1081</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>2611</v>
+        <v>1407</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>3176</v>
+        <v>1638</v>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr"/>
@@ -1568,22 +1568,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>원익QNC</t>
+          <t>유진테크</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>074600</t>
+          <t>084370</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1081</v>
+        <v>1027</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>1407</v>
+        <v>1319</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1638</v>
+        <v>1390</v>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="inlineStr"/>
@@ -1595,22 +1595,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>유진테크</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>084370</t>
+          <t>102710</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>1027</v>
+        <v>823</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>1319</v>
+        <v>1181</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1390</v>
+        <v>1670</v>
       </c>
       <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="inlineStr"/>
@@ -1622,22 +1622,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>102710</t>
+          <t>039030</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>823</v>
+        <v>1953</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>1181</v>
+        <v>2540</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1670</v>
+        <v>3193</v>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="inlineStr"/>
@@ -1649,22 +1649,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>제이엔티씨</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>039030</t>
+          <t>204270</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1953</v>
+        <v>540</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>2540</v>
+        <v>1637</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>3193</v>
+        <v>1920</v>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="inlineStr"/>
@@ -1676,22 +1676,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>제이엔티씨</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>281820</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>540</v>
+        <v>1462</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>1637</v>
+        <v>2011</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1920</v>
+        <v>2170</v>
       </c>
       <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="inlineStr"/>
@@ -1703,22 +1703,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>케이씨텍</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>281820</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1462</v>
+        <v>1289</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>2011</v>
+        <v>1707</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>2170</v>
+        <v>2083</v>
       </c>
       <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr"/>
@@ -1730,22 +1730,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>테크윙</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>089030</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1289</v>
+        <v>985</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>1707</v>
+        <v>1729</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>2083</v>
+        <v>2310</v>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="inlineStr"/>
@@ -1757,22 +1757,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>테크윙</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>089030</t>
+          <t>064760</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>985</v>
+        <v>1258</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>1729</v>
+        <v>1660</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>2310</v>
+        <v>2109</v>
       </c>
       <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="inlineStr"/>
@@ -1784,22 +1784,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>064760</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>1258</v>
+        <v>1505</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>1660</v>
+        <v>1921</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>2109</v>
+        <v>2355</v>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="inlineStr"/>
@@ -1811,22 +1811,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>440110</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1505</v>
+        <v>448</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>1921</v>
+        <v>1264</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>2355</v>
+        <v>2175</v>
       </c>
       <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="inlineStr"/>
@@ -1838,22 +1838,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>파라다이스</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>440110</t>
+          <t>034230</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>448</v>
+        <v>1881</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>1264</v>
+        <v>2277</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>2175</v>
+        <v>2479</v>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="inlineStr"/>
@@ -1865,22 +1865,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>파라다이스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>034230</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>1881</v>
+        <v>2655</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>2277</v>
+        <v>3278</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>2479</v>
+        <v>3920</v>
       </c>
       <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="inlineStr"/>
@@ -1892,22 +1892,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>2655</v>
+        <v>624</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>3278</v>
+        <v>733</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>3920</v>
+        <v>750</v>
       </c>
       <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="inlineStr"/>
@@ -1919,22 +1919,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>624</v>
+        <v>1723</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>733</v>
+        <v>2116</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>750</v>
+        <v>2463</v>
       </c>
       <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="inlineStr"/>
@@ -1946,22 +1946,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>1723</v>
+        <v>3154</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>2116</v>
+        <v>3785</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>2463</v>
+        <v>4361</v>
       </c>
       <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="inlineStr"/>
@@ -1973,22 +1973,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>166090</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>3154</v>
+        <v>1002</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>3785</v>
+        <v>1335</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>4361</v>
+        <v>1450</v>
       </c>
       <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="inlineStr"/>
@@ -2000,22 +2000,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>013030</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>1002</v>
+        <v>608</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>1335</v>
+        <v>714</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1450</v>
+        <v>726</v>
       </c>
       <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="inlineStr"/>
@@ -2027,22 +2027,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>한국카본</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>013030</t>
+          <t>017960</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>608</v>
+        <v>1798</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>714</v>
+        <v>1964</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>726</v>
+        <v>1947</v>
       </c>
       <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="inlineStr"/>
@@ -2054,22 +2054,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>한국카본</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>017960</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1798</v>
+        <v>4736</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>1964</v>
+        <v>6744</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1947</v>
+        <v>8136</v>
       </c>
       <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="inlineStr"/>
@@ -2081,22 +2081,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>4736</v>
+        <v>2442</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>6744</v>
+        <v>3679</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>8136</v>
+        <v>4513</v>
       </c>
       <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="inlineStr"/>
@@ -2108,22 +2108,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>해성디에스</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>195870</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>2442</v>
+        <v>897</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>3679</v>
+        <v>1283</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>4513</v>
+        <v>1547</v>
       </c>
       <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="inlineStr"/>
@@ -2135,22 +2135,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>해성디에스</t>
+          <t>CJ</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>195870</t>
+          <t>001040</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>897</v>
+        <v>27163</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>1283</v>
+        <v>30337</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1547</v>
+        <v>30852</v>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="inlineStr"/>
@@ -2162,22 +2162,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CJ</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>001040</t>
+          <t>000990</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>27163</v>
+        <v>3627</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>30337</v>
+        <v>4511</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>30852</v>
+        <v>5191</v>
       </c>
       <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="inlineStr"/>
@@ -2189,22 +2189,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>000990</t>
+          <t>009540</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>3627</v>
+        <v>55993</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>4511</v>
+        <v>67225</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>5191</v>
+        <v>77345</v>
       </c>
       <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="inlineStr"/>
@@ -2216,22 +2216,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HD한국조선해양</t>
+          <t>HD현대건설기계</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>009540</t>
+          <t>267270</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>55993</v>
+        <v>6821</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>67225</v>
+        <v>8553</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>77345</v>
+        <v>10362</v>
       </c>
       <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="inlineStr"/>
@@ -2243,22 +2243,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HD현대건설기계</t>
+          <t>HD현대마린솔루션</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>267270</t>
+          <t>443060</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>6821</v>
+        <v>4369</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>8553</v>
+        <v>5517</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>10362</v>
+        <v>6420</v>
       </c>
       <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="inlineStr"/>
@@ -2270,22 +2270,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HD현대마린솔루션</t>
+          <t>HD현대마린엔진</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>443060</t>
+          <t>071970</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>4369</v>
+        <v>1515</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>5517</v>
+        <v>2029</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>6420</v>
+        <v>2509</v>
       </c>
       <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="inlineStr"/>
@@ -2297,22 +2297,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HD현대마린엔진</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>071970</t>
+          <t>403870</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1515</v>
+        <v>1266</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>2029</v>
+        <v>1692</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>2509</v>
+        <v>2054</v>
       </c>
       <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="inlineStr"/>
@@ -2324,22 +2324,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>403870</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>1266</v>
+        <v>16195</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>1692</v>
+        <v>18902</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>2054</v>
+        <v>22131</v>
       </c>
       <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="inlineStr"/>
@@ -2351,22 +2351,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>SNT에너지</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>100840</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>16195</v>
+        <v>1243</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>18902</v>
+        <v>1331</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>22131</v>
+        <v>1407</v>
       </c>
       <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="inlineStr"/>
@@ -2378,22 +2378,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SNT에너지</t>
+          <t>계룡건설</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>100840</t>
+          <t>013580</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>1243</v>
+        <v>1780</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1331</v>
+        <v>2130</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>1407</v>
+        <v>2410</v>
       </c>
       <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="inlineStr"/>
@@ -2405,22 +2405,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>계룡건설</t>
+          <t>현대이지웰</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>013580</t>
+          <t>090850</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>1780</v>
+        <v>260</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>2130</v>
+        <v>280</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>2410</v>
+        <v>300</v>
       </c>
       <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="inlineStr"/>
@@ -2432,22 +2432,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>현대이지웰</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>090850</t>
+          <t>353200</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>260</v>
+        <v>2514</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>280</v>
+        <v>3571</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>300</v>
+        <v>4453</v>
       </c>
       <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="inlineStr"/>

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2455,6 +2455,33 @@
       <c r="I74" s="6" t="inlineStr"/>
       <c r="J74" s="7" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>327260</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>248</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>366</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr"/>
+      <c r="G75" s="4" t="inlineStr"/>
+      <c r="H75" s="5" t="inlineStr"/>
+      <c r="I75" s="6" t="inlineStr"/>
+      <c r="J75" s="7" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2482,6 +2482,33 @@
       <c r="I75" s="6" t="inlineStr"/>
       <c r="J75" s="7" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>HDC</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>012630</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>6860</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>8237</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>8742</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr"/>
+      <c r="H76" s="5" t="inlineStr"/>
+      <c r="I76" s="6" t="inlineStr"/>
+      <c r="J76" s="7" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2509,6 +2509,33 @@
       <c r="I76" s="6" t="inlineStr"/>
       <c r="J76" s="7" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>비에이치아이</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>083650</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>1201</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>1522</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>1928</v>
+      </c>
+      <c r="F77" s="4" t="inlineStr"/>
+      <c r="G77" s="4" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr"/>
+      <c r="I77" s="6" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2536,6 +2536,29 @@
       <c r="I77" s="6" t="inlineStr"/>
       <c r="J77" s="7" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>케이엔제이</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>272110</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>320</v>
+      </c>
+      <c r="D78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr"/>
+      <c r="H78" s="5" t="inlineStr"/>
+      <c r="I78" s="6" t="inlineStr"/>
+      <c r="J78" s="7" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2559,6 +2559,60 @@
       <c r="I78" s="6" t="inlineStr"/>
       <c r="J78" s="7" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>코리아써키트</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>007810</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>1467</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>2229</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>2935</v>
+      </c>
+      <c r="F79" s="4" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr"/>
+      <c r="I79" s="6" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>이수페타시스</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>007660</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>3272</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>4604</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>5890</v>
+      </c>
+      <c r="F80" s="4" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr"/>
+      <c r="I80" s="6" t="inlineStr"/>
+      <c r="J80" s="7" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -2441,20 +2441,24 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>2514</v>
+        <v>2759</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>3571</v>
+        <v>4081</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>4453</v>
+        <v>5068</v>
       </c>
       <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="inlineStr"/>
       <c r="H74" s="5" t="inlineStr"/>
       <c r="I74" s="6" t="inlineStr"/>
       <c r="J74" s="7" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>8/4 추정치 상향</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -1820,20 +1820,24 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>448</v>
+        <v>859</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>1264</v>
+        <v>2158</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>2175</v>
+        <v>2618</v>
       </c>
       <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="6" t="inlineStr"/>
       <c r="J51" s="7" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>8/5 상향</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -18,9 +18,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -94,9 +94,12 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -545,430 +548,417 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>CJ</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>001040</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1896</v>
+        <v>27163</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>3175</v>
+        <v>30337</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>3971</v>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>회사/증권사 컨센서스</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="n">
-        <v>46218</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>예시값 - 실제 컨센서스로 수정</t>
-        </is>
-      </c>
+        <v>30852</v>
+      </c>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="6" t="n"/>
+      <c r="J3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>비에이치</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>090460</t>
+          <t>000990</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1148</v>
+        <v>3627</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1429</v>
+        <v>4511</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1607</v>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="7" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+        <v>5191</v>
+      </c>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>디케이티</t>
+          <t>HDC</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>290550</t>
+          <t>012630</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>313</v>
+        <v>6860</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>568</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+        <v>8237</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>8742</v>
+      </c>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>009540</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>554</v>
+        <v>55993</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>799</v>
+        <v>67225</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1278</v>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="7" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+        <v>77345</v>
+      </c>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>HD현대건설기계</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>267270</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>602</v>
+        <v>6821</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1535</v>
+        <v>8553</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3165</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+        <v>10362</v>
+      </c>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>HD현대마린솔루션</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>443060</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1014</v>
+        <v>4369</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1348</v>
+        <v>5517</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1823</v>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="7" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+        <v>6420</v>
+      </c>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>HD현대마린엔진</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>014680</t>
+          <t>071970</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1889</v>
+        <v>1515</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2374</v>
+        <v>2029</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2983</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+        <v>2509</v>
+      </c>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>005290</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="7" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>403870</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1266</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1692</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>2054</v>
+      </c>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>104830</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>719</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>922</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>1040</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="6" t="inlineStr"/>
-      <c r="J11" s="7" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>061970</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SKC</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>011790</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-605</v>
+        <v>16195</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>845</v>
+        <v>18902</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2399</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="7" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+        <v>22131</v>
+      </c>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>319</v>
+        <v>156</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>427</v>
+        <v>248</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>486</v>
-      </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="7" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+        <v>366</v>
+      </c>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>비씨엔씨</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>146320</t>
+          <t>036540</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>162</v>
+        <v>703</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>219</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="7" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+        <v>897</v>
+      </c>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>OSAT</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>에스앤에스텍</t>
+          <t>SKC</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>101490</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="7" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>011790</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-605</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>845</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>2399</v>
+      </c>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>SNT에너지</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>357780</t>
+          <t>100840</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1941</v>
+        <v>1243</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2518</v>
+        <v>1331</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3133</v>
-      </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="6" t="inlineStr"/>
-      <c r="J16" s="7" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+        <v>1407</v>
+      </c>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>디엔에프</t>
+          <t>경동나비엔</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>092070</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="6" t="inlineStr"/>
-      <c r="J17" s="7" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>009450</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>2377</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>2693</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>3174</v>
+      </c>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>계룡건설</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>013580</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>60</v>
+        <v>1780</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>703</v>
+        <v>2130</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>897</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="6" t="inlineStr"/>
-      <c r="J18" s="7" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>OSAT</t>
-        </is>
-      </c>
+        <v>2410</v>
+      </c>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -990,12 +980,11 @@
       <c r="E19" s="4" t="n">
         <v>620</v>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="7" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1017,210 +1006,204 @@
       <c r="E20" s="4" t="n">
         <v>589</v>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="7" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>061970</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="7" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>353200</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>2759</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>4081</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>5068</v>
+      </c>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>8/4 추정치 상향</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>078350</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="6" t="inlineStr"/>
-      <c r="J22" s="7" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>003490</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>8775</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>20815</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>24999</v>
+      </c>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>089970</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>965</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>1357</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>1554</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="6" t="inlineStr"/>
-      <c r="J23" s="7" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>005290</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>경동나비엔</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>009450</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2377</v>
+        <v>484</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2693</v>
+        <v>1131</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3174</v>
-      </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="6" t="inlineStr"/>
-      <c r="J24" s="7" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+        <v>1335</v>
+      </c>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>디아이</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>003160</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8775</v>
+        <v>967</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>20815</v>
+        <v>1151</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>24999</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="7" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+        <v>1241</v>
+      </c>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="9" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>디아이티</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>131970</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>484</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>1131</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>1335</v>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="7" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>110990</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>디아이</t>
+          <t>디엔에프</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>003160</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>967</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>1151</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>1241</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="7" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>092070</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>디아이티</t>
+          <t>디케이티</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>110990</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr"/>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="6" t="inlineStr"/>
-      <c r="J28" s="7" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>290550</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>313</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>568</v>
+      </c>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="9" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1242,1385 +1225,1350 @@
       <c r="E29" s="4" t="n">
         <v>2685</v>
       </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="6" t="inlineStr"/>
-      <c r="J29" s="7" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2517</v>
+        <v>965</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3337</v>
+        <v>1357</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4247</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="6" t="inlineStr"/>
-      <c r="J30" s="7" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+        <v>1554</v>
+      </c>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="9" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>비씨엔씨</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>146320</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>861</v>
+        <v>93</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1010</v>
+        <v>162</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1056</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="7" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+        <v>219</v>
+      </c>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="9" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>비에이치</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>090460</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2750</v>
+        <v>1148</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3532</v>
+        <v>1429</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4124</v>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="7" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+        <v>1607</v>
+      </c>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="9" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>싸이맥스</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>160980</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>260</v>
+        <v>1201</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="7" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+        <v>1522</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>1928</v>
+      </c>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="9" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>039440</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>751</v>
+        <v>2517</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1306</v>
+        <v>3337</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1341</v>
-      </c>
-      <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="6" t="inlineStr"/>
-      <c r="J34" s="7" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+        <v>4247</v>
+      </c>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="6" t="n"/>
+      <c r="J34" s="9" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>231</v>
+        <v>319</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>371</v>
-      </c>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="6" t="inlineStr"/>
-      <c r="J35" s="7" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+        <v>427</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>486</v>
+      </c>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="9" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>엑시콘</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>092870</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>148</v>
+        <v>861</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="6" t="inlineStr"/>
-      <c r="J36" s="7" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+        <v>1010</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>1056</v>
+      </c>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="6" t="n"/>
+      <c r="J36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>357780</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>650</v>
+        <v>1941</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>1076</v>
+        <v>2518</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1357</v>
-      </c>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="6" t="inlineStr"/>
-      <c r="J37" s="7" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+        <v>3133</v>
+      </c>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="6" t="n"/>
+      <c r="J37" s="9" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1096</v>
+        <v>2750</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>1714</v>
-      </c>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="6" t="inlineStr"/>
-      <c r="J38" s="7" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+        <v>3532</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>4124</v>
+      </c>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="6" t="n"/>
+      <c r="J38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>와이씨</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>232140</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>545</v>
+        <v>1896</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>726</v>
+        <v>3175</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>847</v>
-      </c>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="6" t="inlineStr"/>
-      <c r="J39" s="7" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+        <v>3971</v>
+      </c>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>회사/증권사 컨센서스</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>46218</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>예시값 - 실제 컨센서스로 수정</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>싸이맥스</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>160980</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1861</v>
+        <v>260</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>2611</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>3176</v>
-      </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="6" t="inlineStr"/>
-      <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+        <v>450</v>
+      </c>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="6" t="n"/>
+      <c r="J40" s="9" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>원익QNC</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>074600</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>1081</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>1407</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>1638</v>
-      </c>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="6" t="inlineStr"/>
-      <c r="J41" s="7" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>101490</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="6" t="n"/>
+      <c r="J41" s="9" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>유진테크</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>084370</t>
+          <t>039440</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1027</v>
+        <v>751</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>1319</v>
+        <v>1306</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1390</v>
-      </c>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="6" t="inlineStr"/>
-      <c r="J42" s="7" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+        <v>1341</v>
+      </c>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="6" t="n"/>
+      <c r="J42" s="9" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>102710</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>823</v>
+        <v>231</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>1181</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>1670</v>
-      </c>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="6" t="inlineStr"/>
-      <c r="J43" s="7" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+        <v>371</v>
+      </c>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="6" t="n"/>
+      <c r="J43" s="9" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>엑시콘</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>039030</t>
+          <t>092870</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>1953</v>
+        <v>148</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>2540</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>3193</v>
-      </c>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="4" t="inlineStr"/>
-      <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="6" t="inlineStr"/>
-      <c r="J44" s="7" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+        <v>282</v>
+      </c>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="6" t="n"/>
+      <c r="J44" s="9" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>제이엔티씨</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>540</v>
+        <v>650</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>1637</v>
+        <v>1076</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>1920</v>
-      </c>
-      <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="6" t="inlineStr"/>
-      <c r="J45" s="7" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+        <v>1357</v>
+      </c>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="6" t="n"/>
+      <c r="J45" s="9" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>케이씨텍</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>281820</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1462</v>
+        <v>1096</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>2011</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>2170</v>
-      </c>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="6" t="inlineStr"/>
-      <c r="J46" s="7" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+        <v>1714</v>
+      </c>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="6" t="n"/>
+      <c r="J46" s="9" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>와이씨</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>232140</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1289</v>
+        <v>545</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>1707</v>
+        <v>726</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>2083</v>
-      </c>
-      <c r="F47" s="4" t="inlineStr"/>
-      <c r="G47" s="4" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="6" t="inlineStr"/>
-      <c r="J47" s="7" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+        <v>847</v>
+      </c>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="6" t="n"/>
+      <c r="J47" s="9" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>테크윙</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>089030</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>985</v>
+        <v>1861</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>1729</v>
+        <v>2611</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>2310</v>
-      </c>
-      <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="4" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="6" t="inlineStr"/>
-      <c r="J48" s="7" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+        <v>3176</v>
+      </c>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="6" t="n"/>
+      <c r="J48" s="9" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>원익QNC</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>064760</t>
+          <t>074600</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1258</v>
+        <v>1081</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>1660</v>
+        <v>1407</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>2109</v>
-      </c>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="6" t="inlineStr"/>
-      <c r="J49" s="7" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+        <v>1638</v>
+      </c>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="6" t="n"/>
+      <c r="J49" s="9" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>104830</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>1505</v>
+        <v>719</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>1921</v>
+        <v>922</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>2355</v>
-      </c>
-      <c r="F50" s="4" t="inlineStr"/>
-      <c r="G50" s="4" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="6" t="inlineStr"/>
-      <c r="J50" s="7" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+        <v>1040</v>
+      </c>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="6" t="n"/>
+      <c r="J50" s="9" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>유진테크</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>440110</t>
+          <t>084370</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>859</v>
+        <v>1027</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>2158</v>
+        <v>1319</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>2618</v>
-      </c>
-      <c r="F51" s="4" t="inlineStr"/>
-      <c r="G51" s="4" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="6" t="inlineStr"/>
-      <c r="J51" s="7" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>8/5 상향</t>
-        </is>
-      </c>
+        <v>1390</v>
+      </c>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="6" t="n"/>
+      <c r="J51" s="9" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>파라다이스</t>
+          <t>이수페타시스</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>034230</t>
+          <t>007660</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>1881</v>
+        <v>3272</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>2277</v>
+        <v>4604</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>2479</v>
-      </c>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="4" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="6" t="inlineStr"/>
-      <c r="J52" s="7" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+        <v>5890</v>
+      </c>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="6" t="n"/>
+      <c r="J52" s="9" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>102710</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>2655</v>
+        <v>823</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>3278</v>
+        <v>1181</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>3920</v>
-      </c>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="4" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="6" t="inlineStr"/>
-      <c r="J53" s="7" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+        <v>1670</v>
+      </c>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="6" t="n"/>
+      <c r="J53" s="9" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>039030</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>624</v>
+        <v>1953</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>733</v>
+        <v>2540</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>750</v>
-      </c>
-      <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="4" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="6" t="inlineStr"/>
-      <c r="J54" s="7" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+        <v>3193</v>
+      </c>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="6" t="n"/>
+      <c r="J54" s="9" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>제이엔티씨</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>204270</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1723</v>
+        <v>540</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>2116</v>
+        <v>1637</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>2463</v>
-      </c>
-      <c r="F55" s="4" t="inlineStr"/>
-      <c r="G55" s="4" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="6" t="inlineStr"/>
-      <c r="J55" s="7" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+        <v>1920</v>
+      </c>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="4" t="n"/>
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="6" t="n"/>
+      <c r="J55" s="9" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>3154</v>
+        <v>602</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>3785</v>
+        <v>1535</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F56" s="4" t="inlineStr"/>
-      <c r="G56" s="4" t="inlineStr"/>
-      <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="6" t="inlineStr"/>
-      <c r="J56" s="7" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+        <v>3165</v>
+      </c>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="6" t="n"/>
+      <c r="J56" s="9" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>281820</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1002</v>
+        <v>1462</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>1335</v>
+        <v>2011</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="F57" s="4" t="inlineStr"/>
-      <c r="G57" s="4" t="inlineStr"/>
-      <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="6" t="inlineStr"/>
-      <c r="J57" s="7" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+        <v>2170</v>
+      </c>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="4" t="n"/>
+      <c r="H57" s="8" t="n"/>
+      <c r="I57" s="6" t="n"/>
+      <c r="J57" s="9" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>케이엔제이</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>013030</t>
+          <t>272110</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>608</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>714</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>726</v>
-      </c>
-      <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr"/>
-      <c r="H58" s="5" t="inlineStr"/>
-      <c r="I58" s="6" t="inlineStr"/>
-      <c r="J58" s="7" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+        <v>320</v>
+      </c>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="8" t="n"/>
+      <c r="I58" s="6" t="n"/>
+      <c r="J58" s="9" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>한국카본</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>017960</t>
+          <t>007810</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1798</v>
+        <v>1467</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>1964</v>
+        <v>2229</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1947</v>
-      </c>
-      <c r="F59" s="4" t="inlineStr"/>
-      <c r="G59" s="4" t="inlineStr"/>
-      <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="6" t="inlineStr"/>
-      <c r="J59" s="7" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+        <v>2935</v>
+      </c>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="4" t="n"/>
+      <c r="H59" s="8" t="n"/>
+      <c r="I59" s="6" t="n"/>
+      <c r="J59" s="9" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>4736</v>
+        <v>1289</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>6744</v>
+        <v>1707</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>8136</v>
-      </c>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="4" t="inlineStr"/>
-      <c r="H60" s="5" t="inlineStr"/>
-      <c r="I60" s="6" t="inlineStr"/>
-      <c r="J60" s="7" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+        <v>2083</v>
+      </c>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="4" t="n"/>
+      <c r="H60" s="8" t="n"/>
+      <c r="I60" s="6" t="n"/>
+      <c r="J60" s="9" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>2442</v>
+        <v>1014</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>3679</v>
+        <v>1348</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>4513</v>
-      </c>
-      <c r="F61" s="4" t="inlineStr"/>
-      <c r="G61" s="4" t="inlineStr"/>
-      <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="6" t="inlineStr"/>
-      <c r="J61" s="7" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+        <v>1823</v>
+      </c>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="8" t="n"/>
+      <c r="I61" s="6" t="n"/>
+      <c r="J61" s="9" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>해성디에스</t>
+          <t>테크윙</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>195870</t>
+          <t>089030</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>897</v>
+        <v>985</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>1283</v>
+        <v>1729</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1547</v>
-      </c>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr"/>
-      <c r="H62" s="5" t="inlineStr"/>
-      <c r="I62" s="6" t="inlineStr"/>
-      <c r="J62" s="7" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+        <v>2310</v>
+      </c>
+      <c r="F62" s="4" t="n"/>
+      <c r="G62" s="4" t="n"/>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="6" t="n"/>
+      <c r="J62" s="9" t="n"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CJ</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>001040</t>
+          <t>064760</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>27163</v>
+        <v>1258</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>30337</v>
+        <v>1660</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>30852</v>
-      </c>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr"/>
-      <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="6" t="inlineStr"/>
-      <c r="J63" s="7" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+        <v>2109</v>
+      </c>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="8" t="n"/>
+      <c r="I63" s="6" t="n"/>
+      <c r="J63" s="9" t="n"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>000990</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>3627</v>
+        <v>1505</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>4511</v>
+        <v>1921</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>5191</v>
-      </c>
-      <c r="F64" s="4" t="inlineStr"/>
-      <c r="G64" s="4" t="inlineStr"/>
-      <c r="H64" s="5" t="inlineStr"/>
-      <c r="I64" s="6" t="inlineStr"/>
-      <c r="J64" s="7" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+        <v>2355</v>
+      </c>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="6" t="n"/>
+      <c r="J64" s="9" t="n"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HD한국조선해양</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>009540</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>55993</v>
+        <v>554</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>67225</v>
+        <v>799</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>77345</v>
-      </c>
-      <c r="F65" s="4" t="inlineStr"/>
-      <c r="G65" s="4" t="inlineStr"/>
-      <c r="H65" s="5" t="inlineStr"/>
-      <c r="I65" s="6" t="inlineStr"/>
-      <c r="J65" s="7" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+        <v>1278</v>
+      </c>
+      <c r="F65" s="4" t="n"/>
+      <c r="G65" s="4" t="n"/>
+      <c r="H65" s="8" t="n"/>
+      <c r="I65" s="6" t="n"/>
+      <c r="J65" s="9" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HD현대건설기계</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>267270</t>
+          <t>440110</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>6821</v>
+        <v>859</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>8553</v>
+        <v>2158</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>10362</v>
-      </c>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr"/>
-      <c r="H66" s="5" t="inlineStr"/>
-      <c r="I66" s="6" t="inlineStr"/>
-      <c r="J66" s="7" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+        <v>2618</v>
+      </c>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="8" t="n"/>
+      <c r="I66" s="6" t="n"/>
+      <c r="J66" s="9" t="n"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>8/5 상향</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HD현대마린솔루션</t>
+          <t>파라다이스</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>443060</t>
+          <t>034230</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>4369</v>
+        <v>1881</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>5517</v>
+        <v>2277</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>6420</v>
-      </c>
-      <c r="F67" s="4" t="inlineStr"/>
-      <c r="G67" s="4" t="inlineStr"/>
-      <c r="H67" s="5" t="inlineStr"/>
-      <c r="I67" s="6" t="inlineStr"/>
-      <c r="J67" s="7" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+        <v>2479</v>
+      </c>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="4" t="n"/>
+      <c r="H67" s="8" t="n"/>
+      <c r="I67" s="6" t="n"/>
+      <c r="J67" s="9" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HD현대마린엔진</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>071970</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1515</v>
+        <v>2655</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>2029</v>
+        <v>3278</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>2509</v>
-      </c>
-      <c r="F68" s="4" t="inlineStr"/>
-      <c r="G68" s="4" t="inlineStr"/>
-      <c r="H68" s="5" t="inlineStr"/>
-      <c r="I68" s="6" t="inlineStr"/>
-      <c r="J68" s="7" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+        <v>3920</v>
+      </c>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="4" t="n"/>
+      <c r="H68" s="8" t="n"/>
+      <c r="I68" s="6" t="n"/>
+      <c r="J68" s="9" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>403870</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1266</v>
+        <v>624</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>1692</v>
+        <v>733</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>2054</v>
-      </c>
-      <c r="F69" s="4" t="inlineStr"/>
-      <c r="G69" s="4" t="inlineStr"/>
-      <c r="H69" s="5" t="inlineStr"/>
-      <c r="I69" s="6" t="inlineStr"/>
-      <c r="J69" s="7" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+        <v>750</v>
+      </c>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="6" t="n"/>
+      <c r="J69" s="9" t="n"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>16195</v>
+        <v>1723</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>18902</v>
+        <v>2116</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>22131</v>
-      </c>
-      <c r="F70" s="4" t="inlineStr"/>
-      <c r="G70" s="4" t="inlineStr"/>
-      <c r="H70" s="5" t="inlineStr"/>
-      <c r="I70" s="6" t="inlineStr"/>
-      <c r="J70" s="7" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+        <v>2463</v>
+      </c>
+      <c r="F70" s="4" t="n"/>
+      <c r="G70" s="4" t="n"/>
+      <c r="H70" s="8" t="n"/>
+      <c r="I70" s="6" t="n"/>
+      <c r="J70" s="9" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SNT에너지</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>100840</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>1243</v>
+        <v>3154</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>1331</v>
+        <v>3785</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>1407</v>
-      </c>
-      <c r="F71" s="4" t="inlineStr"/>
-      <c r="G71" s="4" t="inlineStr"/>
-      <c r="H71" s="5" t="inlineStr"/>
-      <c r="I71" s="6" t="inlineStr"/>
-      <c r="J71" s="7" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+        <v>4361</v>
+      </c>
+      <c r="F71" s="4" t="n"/>
+      <c r="G71" s="4" t="n"/>
+      <c r="H71" s="8" t="n"/>
+      <c r="I71" s="6" t="n"/>
+      <c r="J71" s="9" t="n"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>계룡건설</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>013580</t>
+          <t>166090</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>1780</v>
+        <v>1002</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>2130</v>
+        <v>1335</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>2410</v>
-      </c>
-      <c r="F72" s="4" t="inlineStr"/>
-      <c r="G72" s="4" t="inlineStr"/>
-      <c r="H72" s="5" t="inlineStr"/>
-      <c r="I72" s="6" t="inlineStr"/>
-      <c r="J72" s="7" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+        <v>1450</v>
+      </c>
+      <c r="F72" s="4" t="n"/>
+      <c r="G72" s="4" t="n"/>
+      <c r="H72" s="8" t="n"/>
+      <c r="I72" s="6" t="n"/>
+      <c r="J72" s="9" t="n"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>현대이지웰</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>090850</t>
+          <t>013030</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>260</v>
+        <v>608</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>280</v>
+        <v>714</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="F73" s="4" t="inlineStr"/>
-      <c r="G73" s="4" t="inlineStr"/>
-      <c r="H73" s="5" t="inlineStr"/>
-      <c r="I73" s="6" t="inlineStr"/>
-      <c r="J73" s="7" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+        <v>726</v>
+      </c>
+      <c r="F73" s="4" t="n"/>
+      <c r="G73" s="4" t="n"/>
+      <c r="H73" s="8" t="n"/>
+      <c r="I73" s="6" t="n"/>
+      <c r="J73" s="9" t="n"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>한국카본</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>017960</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>2759</v>
+        <v>1798</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>4081</v>
+        <v>1964</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>5068</v>
-      </c>
-      <c r="F74" s="4" t="inlineStr"/>
-      <c r="G74" s="4" t="inlineStr"/>
-      <c r="H74" s="5" t="inlineStr"/>
-      <c r="I74" s="6" t="inlineStr"/>
-      <c r="J74" s="7" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>8/4 추정치 상향</t>
-        </is>
-      </c>
+        <v>1947</v>
+      </c>
+      <c r="F74" s="4" t="n"/>
+      <c r="G74" s="4" t="n"/>
+      <c r="H74" s="8" t="n"/>
+      <c r="I74" s="6" t="n"/>
+      <c r="J74" s="9" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>156</v>
+        <v>4736</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>248</v>
+        <v>6744</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>366</v>
-      </c>
-      <c r="F75" s="4" t="inlineStr"/>
-      <c r="G75" s="4" t="inlineStr"/>
-      <c r="H75" s="5" t="inlineStr"/>
-      <c r="I75" s="6" t="inlineStr"/>
-      <c r="J75" s="7" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+        <v>8136</v>
+      </c>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="8" t="n"/>
+      <c r="I75" s="6" t="n"/>
+      <c r="J75" s="9" t="n"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HDC</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>012630</t>
+          <t>014680</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>6860</v>
+        <v>1889</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>8237</v>
+        <v>2374</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>8742</v>
-      </c>
-      <c r="F76" s="4" t="inlineStr"/>
-      <c r="G76" s="4" t="inlineStr"/>
-      <c r="H76" s="5" t="inlineStr"/>
-      <c r="I76" s="6" t="inlineStr"/>
-      <c r="J76" s="7" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+        <v>2983</v>
+      </c>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="6" t="n"/>
+      <c r="J76" s="9" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>083650</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="n">
-        <v>1201</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>1522</v>
-      </c>
-      <c r="E77" s="4" t="n">
-        <v>1928</v>
-      </c>
-      <c r="F77" s="4" t="inlineStr"/>
-      <c r="G77" s="4" t="inlineStr"/>
-      <c r="H77" s="5" t="inlineStr"/>
-      <c r="I77" s="6" t="inlineStr"/>
-      <c r="J77" s="7" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+          <t>078350</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="4" t="n"/>
+      <c r="E77" s="4" t="n"/>
+      <c r="F77" s="4" t="n"/>
+      <c r="G77" s="4" t="n"/>
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="6" t="n"/>
+      <c r="J77" s="9" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>케이엔제이</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>272110</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>320</v>
-      </c>
-      <c r="D78" s="4" t="inlineStr"/>
-      <c r="E78" s="4" t="inlineStr"/>
-      <c r="F78" s="4" t="inlineStr"/>
-      <c r="G78" s="4" t="inlineStr"/>
-      <c r="H78" s="5" t="inlineStr"/>
-      <c r="I78" s="6" t="inlineStr"/>
-      <c r="J78" s="7" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+        <v>2442</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>3679</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>4513</v>
+      </c>
+      <c r="F78" s="4" t="n"/>
+      <c r="G78" s="4" t="n"/>
+      <c r="H78" s="8" t="n"/>
+      <c r="I78" s="6" t="n"/>
+      <c r="J78" s="9" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>해성디에스</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>195870</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1467</v>
+        <v>897</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>2229</v>
+        <v>1283</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>2935</v>
-      </c>
-      <c r="F79" s="4" t="inlineStr"/>
-      <c r="G79" s="4" t="inlineStr"/>
-      <c r="H79" s="5" t="inlineStr"/>
-      <c r="I79" s="6" t="inlineStr"/>
-      <c r="J79" s="7" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+        <v>1547</v>
+      </c>
+      <c r="F79" s="4" t="n"/>
+      <c r="G79" s="4" t="n"/>
+      <c r="H79" s="8" t="n"/>
+      <c r="I79" s="6" t="n"/>
+      <c r="J79" s="9" t="n"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>이수페타시스</t>
+          <t>현대이지웰</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>007660</t>
+          <t>090850</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>3272</v>
+        <v>260</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>4604</v>
+        <v>280</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>5890</v>
-      </c>
-      <c r="F80" s="4" t="inlineStr"/>
-      <c r="G80" s="4" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr"/>
-      <c r="I80" s="6" t="inlineStr"/>
-      <c r="J80" s="7" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="F80" s="4" t="n"/>
+      <c r="G80" s="4" t="n"/>
+      <c r="H80" s="8" t="n"/>
+      <c r="I80" s="6" t="n"/>
+      <c r="J80" s="9" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>isc</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1036</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1445</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1829</v>
+      </c>
+      <c r="J81" s="10" t="n">
+        <v>46239</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -2557,6 +2557,11 @@
           <t>isc</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>095340</t>
+        </is>
+      </c>
       <c r="C81" t="n">
         <v>1036</v>
       </c>

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -652,7 +652,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HD현대건설기계</t>
+          <t>HD건설기계</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6821</v>
+        <v>7602</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8553</v>
+        <v>9271</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10362</v>
+        <v>10904</v>
       </c>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
@@ -911,48 +911,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>경동나비엔</t>
+          <t>isc</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>009450</t>
+          <t>095340</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2377</v>
+        <v>1036</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2693</v>
+        <v>1445</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3174</v>
+        <v>1829</v>
       </c>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="8" t="n"/>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="9" t="n"/>
+      <c r="J17" s="9" t="n">
+        <v>46239</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>계룡건설</t>
+          <t>경동나비엔</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>013580</t>
+          <t>009450</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1780</v>
+        <v>2377</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2130</v>
+        <v>2693</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2410</v>
+        <v>3174</v>
       </c>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
@@ -963,22 +965,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>계룡건설</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>033640</t>
+          <t>013580</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>411</v>
+        <v>1780</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>522</v>
+        <v>2130</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>620</v>
+        <v>2410</v>
       </c>
       <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n"/>
@@ -989,22 +991,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>네패스아크</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>330860</t>
+          <t>033640</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>269</v>
+        <v>411</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>442</v>
+        <v>522</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>589</v>
+        <v>620</v>
       </c>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
@@ -1015,74 +1017,80 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>네패스아크</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>330860</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2759</v>
+        <v>269</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>4081</v>
+        <v>442</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5068</v>
+        <v>589</v>
       </c>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="8" t="n"/>
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="9" t="n"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>8/4 추정치 상향</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>353200</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>8775</v>
+        <v>2759</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>20815</v>
+        <v>4081</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>24999</v>
+        <v>5068</v>
       </c>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="8" t="n"/>
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="9" t="n"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>8/4 추정치 상향</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>005290</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
+          <t>003490</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>8775</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>20815</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>24999</v>
+      </c>
       <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="8" t="n"/>
@@ -1092,23 +1100,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>131970</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>484</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1131</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>1335</v>
-      </c>
+          <t>005290</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="8" t="n"/>
@@ -1118,22 +1120,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>디아이</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>003160</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>967</v>
+        <v>484</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1151</v>
+        <v>1131</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1241</v>
+        <v>1335</v>
       </c>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
@@ -1144,17 +1146,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>디아이티</t>
+          <t>디아이</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>110990</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
+          <t>003160</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>967</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>1151</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>1241</v>
+      </c>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="8" t="n"/>
@@ -1164,12 +1172,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>디엔에프</t>
+          <t>디아이티</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>092070</t>
+          <t>110990</t>
         </is>
       </c>
       <c r="C27" s="4" t="n"/>
@@ -1184,20 +1192,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>디케이티</t>
+          <t>디엔에프</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>290550</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>313</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>568</v>
-      </c>
+          <t>092070</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
@@ -1208,23 +1212,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>롯데관광개발</t>
+          <t>디케이티</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>032350</t>
+          <t>290550</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1995</v>
+        <v>313</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2425</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>2685</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="8" t="n"/>
@@ -1234,22 +1236,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>롯데관광개발</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>089970</t>
+          <t>032350</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>965</v>
+        <v>1995</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1357</v>
+        <v>2425</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1554</v>
+        <v>2685</v>
       </c>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
@@ -1260,22 +1262,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>비씨엔씨</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>146320</t>
+          <t>089970</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>93</v>
+        <v>965</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>162</v>
+        <v>1357</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>219</v>
+        <v>1554</v>
       </c>
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
@@ -1286,22 +1288,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>비에이치</t>
+          <t>비씨엔씨</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>090460</t>
+          <t>146320</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1148</v>
+        <v>93</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1429</v>
+        <v>162</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1607</v>
+        <v>219</v>
       </c>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
@@ -1312,22 +1314,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>비에이치아이</t>
+          <t>비에이치</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>083650</t>
+          <t>090460</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1201</v>
+        <v>1148</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1522</v>
+        <v>1429</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1928</v>
+        <v>1607</v>
       </c>
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
@@ -1338,22 +1340,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>비에이치아이</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>083650</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2517</v>
+        <v>1201</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3337</v>
+        <v>1522</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4247</v>
+        <v>1928</v>
       </c>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
@@ -1364,22 +1366,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>319</v>
+        <v>2517</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>427</v>
+        <v>3337</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>486</v>
+        <v>4247</v>
       </c>
       <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
@@ -1390,22 +1392,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>세진중공업</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>075580</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>861</v>
+        <v>319</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>1010</v>
+        <v>427</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1056</v>
+        <v>486</v>
       </c>
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
@@ -1416,22 +1418,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>세진중공업</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>357780</t>
+          <t>075580</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1941</v>
+        <v>861</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>2518</v>
+        <v>1010</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>3133</v>
+        <v>1056</v>
       </c>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
@@ -1442,22 +1444,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>357780</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>2750</v>
+        <v>1941</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>3532</v>
+        <v>2518</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>4124</v>
+        <v>3133</v>
       </c>
       <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
@@ -1468,79 +1470,85 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1896</v>
+        <v>2750</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>3175</v>
+        <v>3532</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>3971</v>
+        <v>4124</v>
       </c>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
-      <c r="H39" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>회사/증권사 컨센서스</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="n">
-        <v>46218</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>예시값 - 실제 컨센서스로 수정</t>
-        </is>
-      </c>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="6" t="n"/>
+      <c r="J39" s="9" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>싸이맥스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>160980</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>260</v>
+        <v>1896</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="E40" s="4" t="n"/>
+        <v>3175</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>3971</v>
+      </c>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="6" t="n"/>
-      <c r="J40" s="9" t="n"/>
+      <c r="H40" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>회사/증권사 컨센서스</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>46218</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>예시값 - 실제 컨센서스로 수정</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>에스앤에스텍</t>
+          <t>싸이맥스</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>101490</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
+          <t>160980</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>450</v>
+      </c>
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
@@ -1551,23 +1559,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>039440</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>751</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>1306</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>1341</v>
-      </c>
+          <t>101490</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="n"/>
       <c r="H42" s="8" t="n"/>
@@ -1577,21 +1579,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>039440</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>231</v>
+        <v>751</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>371</v>
-      </c>
-      <c r="E43" s="4" t="n"/>
+        <v>1306</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>1341</v>
+      </c>
       <c r="F43" s="4" t="n"/>
       <c r="G43" s="4" t="n"/>
       <c r="H43" s="8" t="n"/>
@@ -1601,19 +1605,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>엑시콘</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>092870</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>148</v>
+        <v>231</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>282</v>
+        <v>371</v>
       </c>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
@@ -1625,23 +1629,21 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>엑시콘</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>092870</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>650</v>
+        <v>148</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>1076</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>1357</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="8" t="n"/>
@@ -1651,21 +1653,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>033160</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1096</v>
+        <v>650</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>1714</v>
-      </c>
-      <c r="E46" s="4" t="n"/>
+        <v>1076</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>1357</v>
+      </c>
       <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="8" t="n"/>
@@ -1675,23 +1679,21 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>와이씨</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>232140</t>
+          <t>033160</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>545</v>
+        <v>1096</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>726</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>847</v>
-      </c>
+        <v>1714</v>
+      </c>
+      <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="8" t="n"/>
@@ -1701,22 +1703,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>와이씨</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>240810</t>
+          <t>232140</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1861</v>
+        <v>545</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>2611</v>
+        <v>726</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>3176</v>
+        <v>847</v>
       </c>
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
@@ -1727,22 +1729,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>원익QNC</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>074600</t>
+          <t>240810</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1081</v>
+        <v>1861</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>1407</v>
+        <v>2611</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1638</v>
+        <v>3176</v>
       </c>
       <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
@@ -1753,22 +1755,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>원익QNC</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>104830</t>
+          <t>074600</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>719</v>
+        <v>1081</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>922</v>
+        <v>1407</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1040</v>
+        <v>1638</v>
       </c>
       <c r="F50" s="4" t="n"/>
       <c r="G50" s="4" t="n"/>
@@ -1779,22 +1781,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>유진테크</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>084370</t>
+          <t>104830</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1027</v>
+        <v>719</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>1319</v>
+        <v>922</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1390</v>
+        <v>1040</v>
       </c>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n"/>
@@ -1805,22 +1807,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>이수페타시스</t>
+          <t>유진테크</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>007660</t>
+          <t>084370</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>3272</v>
+        <v>1027</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>4604</v>
+        <v>1319</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>5890</v>
+        <v>1390</v>
       </c>
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
@@ -1831,22 +1833,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>이수페타시스</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>102710</t>
+          <t>007660</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>823</v>
+        <v>3272</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>1181</v>
+        <v>4604</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1670</v>
+        <v>5890</v>
       </c>
       <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
@@ -1857,22 +1859,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>039030</t>
+          <t>102710</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1953</v>
+        <v>823</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>2540</v>
+        <v>1181</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>3193</v>
+        <v>1670</v>
       </c>
       <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n"/>
@@ -1883,22 +1885,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>제이엔티씨</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>039030</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>540</v>
+        <v>1953</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>1637</v>
+        <v>2540</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1920</v>
+        <v>3193</v>
       </c>
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n"/>
@@ -1909,22 +1911,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>제이엔티씨</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>204270</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>602</v>
+        <v>540</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>1535</v>
+        <v>1637</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>3165</v>
+        <v>1920</v>
       </c>
       <c r="F56" s="4" t="n"/>
       <c r="G56" s="4" t="n"/>
@@ -1935,22 +1937,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>케이씨텍</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>281820</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1462</v>
+        <v>602</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>2011</v>
+        <v>1535</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>2170</v>
+        <v>3165</v>
       </c>
       <c r="F57" s="4" t="n"/>
       <c r="G57" s="4" t="n"/>
@@ -1961,19 +1963,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>케이엔제이</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>272110</t>
+          <t>281820</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>320</v>
-      </c>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
+        <v>1462</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>2170</v>
+      </c>
       <c r="F58" s="4" t="n"/>
       <c r="G58" s="4" t="n"/>
       <c r="H58" s="8" t="n"/>
@@ -1983,23 +1989,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>케이엔제이</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>272110</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1467</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>2229</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>2935</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="8" t="n"/>
@@ -2009,22 +2011,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>007810</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1289</v>
+        <v>1467</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>1707</v>
+        <v>2229</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>2083</v>
+        <v>2935</v>
       </c>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
@@ -2035,22 +2037,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1014</v>
+        <v>1289</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1348</v>
+        <v>1707</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1823</v>
+        <v>2083</v>
       </c>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
@@ -2061,22 +2063,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>테크윙</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>089030</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>985</v>
+        <v>1014</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>1729</v>
+        <v>1348</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>2310</v>
+        <v>1823</v>
       </c>
       <c r="F62" s="4" t="n"/>
       <c r="G62" s="4" t="n"/>
@@ -2087,22 +2089,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>테크윙</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>064760</t>
+          <t>089030</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1258</v>
+        <v>985</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>1660</v>
+        <v>1729</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>2109</v>
+        <v>2310</v>
       </c>
       <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n"/>
@@ -2113,22 +2115,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>064760</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1505</v>
+        <v>1258</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>1921</v>
+        <v>1660</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>2355</v>
+        <v>2109</v>
       </c>
       <c r="F64" s="4" t="n"/>
       <c r="G64" s="4" t="n"/>
@@ -2139,22 +2141,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>554</v>
+        <v>1505</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>799</v>
+        <v>1921</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1278</v>
+        <v>2355</v>
       </c>
       <c r="F65" s="4" t="n"/>
       <c r="G65" s="4" t="n"/>
@@ -2165,79 +2167,79 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>440110</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>859</v>
+        <v>554</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>2158</v>
+        <v>799</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>2618</v>
+        <v>1278</v>
       </c>
       <c r="F66" s="4" t="n"/>
       <c r="G66" s="4" t="n"/>
       <c r="H66" s="8" t="n"/>
       <c r="I66" s="6" t="n"/>
       <c r="J66" s="9" t="n"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>8/5 상향</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>파라다이스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>034230</t>
+          <t>440110</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>1881</v>
+        <v>859</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>2277</v>
+        <v>2158</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>2479</v>
+        <v>2618</v>
       </c>
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
       <c r="H67" s="8" t="n"/>
       <c r="I67" s="6" t="n"/>
       <c r="J67" s="9" t="n"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>8/5 상향</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>파라다이스</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>034230</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>2655</v>
+        <v>1881</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>3278</v>
+        <v>2277</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>3920</v>
+        <v>2479</v>
       </c>
       <c r="F68" s="4" t="n"/>
       <c r="G68" s="4" t="n"/>
@@ -2248,22 +2250,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>624</v>
+        <v>2655</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>733</v>
+        <v>3278</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>750</v>
+        <v>3920</v>
       </c>
       <c r="F69" s="4" t="n"/>
       <c r="G69" s="4" t="n"/>
@@ -2274,22 +2276,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>1723</v>
+        <v>624</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>2116</v>
+        <v>733</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>2463</v>
+        <v>750</v>
       </c>
       <c r="F70" s="4" t="n"/>
       <c r="G70" s="4" t="n"/>
@@ -2300,22 +2302,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>3154</v>
+        <v>1723</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>3785</v>
+        <v>2116</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>4361</v>
+        <v>2463</v>
       </c>
       <c r="F71" s="4" t="n"/>
       <c r="G71" s="4" t="n"/>
@@ -2326,22 +2328,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>1002</v>
+        <v>3154</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1335</v>
+        <v>3785</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>1450</v>
+        <v>4361</v>
       </c>
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
@@ -2352,22 +2354,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>013030</t>
+          <t>166090</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>608</v>
+        <v>1002</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>714</v>
+        <v>1335</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>726</v>
+        <v>1450</v>
       </c>
       <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
@@ -2378,22 +2380,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>한국카본</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>017960</t>
+          <t>013030</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>1798</v>
+        <v>608</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>1964</v>
+        <v>714</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1947</v>
+        <v>726</v>
       </c>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
@@ -2404,22 +2406,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>한국카본</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>017960</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>4736</v>
+        <v>1798</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>6744</v>
+        <v>1964</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>8136</v>
+        <v>1947</v>
       </c>
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
@@ -2430,22 +2432,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>014680</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>1889</v>
+        <v>4736</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>2374</v>
+        <v>6744</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>2983</v>
+        <v>8136</v>
       </c>
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
@@ -2456,17 +2458,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>078350</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="n"/>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="4" t="n"/>
+          <t>014680</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>1889</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>2374</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>2983</v>
+      </c>
       <c r="F77" s="4" t="n"/>
       <c r="G77" s="4" t="n"/>
       <c r="H77" s="8" t="n"/>
@@ -2476,23 +2484,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>082740</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>2442</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>3679</v>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>4513</v>
-      </c>
+          <t>078350</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n"/>
+      <c r="D78" s="4" t="n"/>
+      <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n"/>
       <c r="H78" s="8" t="n"/>
@@ -2502,22 +2504,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>해성디에스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>195870</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>897</v>
+        <v>2442</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>1283</v>
+        <v>3679</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1547</v>
+        <v>4513</v>
       </c>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
@@ -2528,22 +2530,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>현대이지웰</t>
+          <t>해성디에스</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>090850</t>
+          <t>195870</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>260</v>
+        <v>897</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>280</v>
+        <v>1283</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>300</v>
+        <v>1547</v>
       </c>
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
@@ -2554,26 +2556,24 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>isc</t>
+          <t>현대이지웰</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>095340</t>
+          <t>090850</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1036</v>
+        <v>260</v>
       </c>
       <c r="D81" t="n">
-        <v>1445</v>
+        <v>280</v>
       </c>
       <c r="E81" t="n">
-        <v>1829</v>
-      </c>
-      <c r="J81" s="10" t="n">
-        <v>46239</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="J81" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -626,22 +626,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HD한국조선해양</t>
+          <t>HD건설기계</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>009540</t>
+          <t>267270</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>55993</v>
+        <v>7602</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>67225</v>
+        <v>9271</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>77345</v>
+        <v>10904</v>
       </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
@@ -652,22 +652,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HD건설기계</t>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>267270</t>
+          <t>009540</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7602</v>
+        <v>55993</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9271</v>
+        <v>67225</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10904</v>
+        <v>77345</v>
       </c>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
@@ -1662,19 +1662,30 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>650</v>
+        <v>734</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>1076</v>
+        <v>1174</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1357</v>
+        <v>1545</v>
       </c>
       <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="8" t="n"/>
-      <c r="I46" s="6" t="n"/>
-      <c r="J46" s="9" t="n"/>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">컨센서스 </t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>46254</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>상향 650&gt;734(1회)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2585,6 +2585,24 @@
         <v>300</v>
       </c>
       <c r="J81" s="10" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>제닉</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>123330</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>296</v>
+      </c>
+      <c r="D82" t="n">
+        <v>490</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1922,23 +1922,21 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>제이엔티씨</t>
+          <t>제닉</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>123330</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>540</v>
+        <v>296</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>1637</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>1920</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="E56" s="4" t="n"/>
       <c r="F56" s="4" t="n"/>
       <c r="G56" s="4" t="n"/>
       <c r="H56" s="8" t="n"/>
@@ -1948,22 +1946,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>제이엔티씨</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>204270</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>602</v>
+        <v>540</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>1535</v>
+        <v>1637</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>3165</v>
+        <v>1920</v>
       </c>
       <c r="F57" s="4" t="n"/>
       <c r="G57" s="4" t="n"/>
@@ -1974,22 +1972,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>케이씨텍</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>281820</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>1462</v>
+        <v>602</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>2011</v>
+        <v>1535</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>2170</v>
+        <v>3165</v>
       </c>
       <c r="F58" s="4" t="n"/>
       <c r="G58" s="4" t="n"/>
@@ -2000,19 +1998,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>케이엔제이</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>272110</t>
+          <t>281820</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>320</v>
-      </c>
-      <c r="D59" s="4" t="n"/>
-      <c r="E59" s="4" t="n"/>
+        <v>1462</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>2170</v>
+      </c>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="8" t="n"/>
@@ -2022,23 +2024,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>케이엔제이</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>272110</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1467</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>2229</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>2935</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
       <c r="H60" s="8" t="n"/>
@@ -2048,22 +2046,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>183300</t>
+          <t>007810</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1289</v>
+        <v>1467</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1707</v>
+        <v>2229</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2083</v>
+        <v>2935</v>
       </c>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
@@ -2074,22 +2072,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1014</v>
+        <v>1289</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>1348</v>
+        <v>1707</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1823</v>
+        <v>2083</v>
       </c>
       <c r="F62" s="4" t="n"/>
       <c r="G62" s="4" t="n"/>
@@ -2100,22 +2098,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>테크윙</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>089030</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>985</v>
+        <v>1014</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>1729</v>
+        <v>1348</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>2310</v>
+        <v>1823</v>
       </c>
       <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n"/>
@@ -2126,22 +2124,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>테크윙</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>064760</t>
+          <t>089030</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1258</v>
+        <v>985</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>1660</v>
+        <v>1729</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>2109</v>
+        <v>2310</v>
       </c>
       <c r="F64" s="4" t="n"/>
       <c r="G64" s="4" t="n"/>
@@ -2152,22 +2150,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>064760</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1505</v>
+        <v>1258</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>1921</v>
+        <v>1660</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>2355</v>
+        <v>2109</v>
       </c>
       <c r="F65" s="4" t="n"/>
       <c r="G65" s="4" t="n"/>
@@ -2178,22 +2176,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>554</v>
+        <v>1505</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>799</v>
+        <v>1921</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1278</v>
+        <v>2355</v>
       </c>
       <c r="F66" s="4" t="n"/>
       <c r="G66" s="4" t="n"/>
@@ -2204,79 +2202,79 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>440110</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>859</v>
+        <v>554</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>2158</v>
+        <v>799</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>2618</v>
+        <v>1278</v>
       </c>
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
       <c r="H67" s="8" t="n"/>
       <c r="I67" s="6" t="n"/>
       <c r="J67" s="9" t="n"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>8/5 상향</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>파라다이스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>034230</t>
+          <t>440110</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1881</v>
+        <v>859</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>2277</v>
+        <v>2158</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>2479</v>
+        <v>2618</v>
       </c>
       <c r="F68" s="4" t="n"/>
       <c r="G68" s="4" t="n"/>
       <c r="H68" s="8" t="n"/>
       <c r="I68" s="6" t="n"/>
       <c r="J68" s="9" t="n"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>8/5 상향</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>파라다이스</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>034230</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>2655</v>
+        <v>1881</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>3278</v>
+        <v>2277</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>3920</v>
+        <v>2479</v>
       </c>
       <c r="F69" s="4" t="n"/>
       <c r="G69" s="4" t="n"/>
@@ -2287,22 +2285,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>624</v>
+        <v>2655</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>733</v>
+        <v>3278</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>750</v>
+        <v>3920</v>
       </c>
       <c r="F70" s="4" t="n"/>
       <c r="G70" s="4" t="n"/>
@@ -2313,22 +2311,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>1723</v>
+        <v>624</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>2116</v>
+        <v>733</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>2463</v>
+        <v>750</v>
       </c>
       <c r="F71" s="4" t="n"/>
       <c r="G71" s="4" t="n"/>
@@ -2339,22 +2337,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>067310</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>3154</v>
+        <v>1723</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>3785</v>
+        <v>2116</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>4361</v>
+        <v>2463</v>
       </c>
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
@@ -2365,22 +2363,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>067310</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>1002</v>
+        <v>3154</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>1335</v>
+        <v>3785</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>1450</v>
+        <v>4361</v>
       </c>
       <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
@@ -2391,22 +2389,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>013030</t>
+          <t>166090</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>608</v>
+        <v>1002</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>714</v>
+        <v>1335</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>726</v>
+        <v>1450</v>
       </c>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
@@ -2417,22 +2415,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>한국카본</t>
+          <t>하이록코리아</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>017960</t>
+          <t>013030</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>1798</v>
+        <v>608</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>1964</v>
+        <v>714</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>1947</v>
+        <v>726</v>
       </c>
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
@@ -2443,22 +2441,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>한국카본</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>017960</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>4736</v>
+        <v>1798</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>6744</v>
+        <v>1964</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>8136</v>
+        <v>1947</v>
       </c>
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
@@ -2469,22 +2467,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>014680</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>1889</v>
+        <v>4736</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>2374</v>
+        <v>6744</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>2983</v>
+        <v>8136</v>
       </c>
       <c r="F77" s="4" t="n"/>
       <c r="G77" s="4" t="n"/>
@@ -2495,17 +2493,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>078350</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="n"/>
-      <c r="D78" s="4" t="n"/>
-      <c r="E78" s="4" t="n"/>
+          <t>014680</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>1889</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>2374</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>2983</v>
+      </c>
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n"/>
       <c r="H78" s="8" t="n"/>
@@ -2515,23 +2519,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>082740</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>2442</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>3679</v>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>4513</v>
-      </c>
+          <t>078350</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="4" t="n"/>
+      <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
       <c r="H79" s="8" t="n"/>
@@ -2541,22 +2539,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>해성디에스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>195870</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>897</v>
+        <v>2442</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>1283</v>
+        <v>3679</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>1547</v>
+        <v>4513</v>
       </c>
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
@@ -2567,41 +2565,65 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>현대이지웰</t>
+          <t>해성디에스</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>090850</t>
+          <t>195870</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>260</v>
+        <v>897</v>
       </c>
       <c r="D81" t="n">
-        <v>280</v>
+        <v>1283</v>
       </c>
       <c r="E81" t="n">
-        <v>300</v>
+        <v>1547</v>
       </c>
       <c r="J81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>제닉</t>
+          <t>현대이지웰</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>123330</t>
+          <t>090850</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="D82" t="n">
-        <v>490</v>
+        <v>280</v>
+      </c>
+      <c r="E82" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>하이브</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>352820</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2860</v>
+      </c>
+      <c r="D83" t="n">
+        <v>4871</v>
+      </c>
+      <c r="E83" t="n">
+        <v>5432</v>
       </c>
     </row>
   </sheetData>

--- a/data/consensus.xlsx
+++ b/data/consensus.xlsx
@@ -2441,22 +2441,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>한국카본</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>017960</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>1798</v>
+        <v>2860</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>1964</v>
+        <v>4871</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>1947</v>
+        <v>5432</v>
       </c>
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
@@ -2467,22 +2467,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>한국카본</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>017960</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>4736</v>
+        <v>1798</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>6744</v>
+        <v>1964</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>8136</v>
+        <v>1947</v>
       </c>
       <c r="F77" s="4" t="n"/>
       <c r="G77" s="4" t="n"/>
@@ -2493,22 +2493,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>014680</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>1889</v>
+        <v>4736</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>2374</v>
+        <v>6744</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>2983</v>
+        <v>8136</v>
       </c>
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n"/>
@@ -2519,17 +2519,23 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>078350</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="n"/>
-      <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="n"/>
+          <t>014680</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>1889</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>2374</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>2983</v>
+      </c>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
       <c r="H79" s="8" t="n"/>
@@ -2539,23 +2545,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>082740</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>2442</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>3679</v>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>4513</v>
-      </c>
+          <t>078350</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n"/>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="4" t="n"/>
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
       <c r="H80" s="8" t="n"/>
@@ -2565,65 +2565,65 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>해성디에스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>195870</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>897</v>
+        <v>2442</v>
       </c>
       <c r="D81" t="n">
-        <v>1283</v>
+        <v>3679</v>
       </c>
       <c r="E81" t="n">
-        <v>1547</v>
+        <v>4513</v>
       </c>
       <c r="J81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>현대이지웰</t>
+          <t>해성디에스</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>090850</t>
+          <t>195870</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>260</v>
+        <v>897</v>
       </c>
       <c r="D82" t="n">
-        <v>280</v>
+        <v>1283</v>
       </c>
       <c r="E82" t="n">
-        <v>300</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>현대이지웰</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>090850</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2860</v>
+        <v>260</v>
       </c>
       <c r="D83" t="n">
-        <v>4871</v>
+        <v>280</v>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
